--- a/L3报表项目版本信息.xlsx
+++ b/L3报表项目版本信息.xlsx
@@ -730,7 +730,7 @@
     <row r="2" ht="31.05" customHeight="1" s="17">
       <c r="A2" s="22" t="inlineStr">
         <is>
-          <t>L3报表：KFM选冶厂月度/日报生产指标完成情况，Power BI 项目格式（PBIP）。含报告（PBIR）与语义模型（TMDL）两部分，语言文化 zh-CN。最后更新：2026-10-14</t>
+          <t>L3报表：KFM选冶厂月度/日报生产指标完成情况，Power BI 项目格式（PBIP）。含报告（PBIR）与语义模型（TMDL）两部分，语言文化 zh-CN。最后更新：2026-10-15</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
     <row r="4">
       <c r="A4" s="19" t="inlineStr">
         <is>
-          <t>报告定义版本：2.0.0　｜　共 5 个页面、39 个视觉对象、4 个书签</t>
+          <t>报告定义版本：2.0.0　｜　共 4 个页面、21 个视觉对象、4 个书签</t>
         </is>
       </c>
     </row>
@@ -781,15 +781,15 @@
       <c r="F6" s="15" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="23" t="inlineStr">
-        <is>
-          <t>KFM月报UIE</t>
+      <c r="A7" s="21" t="inlineStr">
+        <is>
+          <t>月报</t>
         </is>
       </c>
       <c r="B7" s="15" t="n"/>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>月报主页（18 个视觉对象）</t>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>月报落地页（7 个视觉对象）</t>
         </is>
       </c>
       <c r="D7" s="14" t="n"/>
@@ -797,15 +797,15 @@
       <c r="F7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="21" t="inlineStr">
-        <is>
-          <t>月报</t>
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>月报数据导出</t>
         </is>
       </c>
       <c r="B8" s="15" t="n"/>
-      <c r="C8" s="13" t="inlineStr">
-        <is>
-          <t>月报落地页（7 个视觉对象）</t>
+      <c r="C8" s="18" t="inlineStr">
+        <is>
+          <t>隐藏页，视图模式下不可见（5 个视觉对象）</t>
         </is>
       </c>
       <c r="D8" s="14" t="n"/>
@@ -815,13 +815,13 @@
     <row r="9">
       <c r="A9" s="23" t="inlineStr">
         <is>
-          <t>数据导出</t>
+          <t>测试</t>
         </is>
       </c>
       <c r="B9" s="15" t="n"/>
       <c r="C9" s="18" t="inlineStr">
         <is>
-          <t>隐藏页，视图模式下不可见（5 个视觉对象）</t>
+          <t>隐藏页，视图模式下不可见（4 个视觉对象）</t>
         </is>
       </c>
       <c r="D9" s="14" t="n"/>
@@ -831,264 +831,253 @@
     <row r="10">
       <c r="A10" s="23" t="inlineStr">
         <is>
-          <t>测试</t>
-        </is>
-      </c>
-      <c r="B10" s="15" t="n"/>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>隐藏页，视图模式下不可见（4 个视觉对象）</t>
-        </is>
-      </c>
+          <t>主题：Fluent2 基础主题 + 自定义主题，注册 2 张背景图片</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="n"/>
+      <c r="C10" s="14" t="n"/>
       <c r="D10" s="14" t="n"/>
       <c r="E10" s="14" t="n"/>
       <c r="F10" s="15" t="n"/>
     </row>
     <row r="11" ht="22.05" customHeight="1" s="17">
-      <c r="A11" s="23" t="inlineStr">
-        <is>
-          <t>主题：Fluent2 基础主题 + 自定义主题，注册 2 张背景图片</t>
-        </is>
-      </c>
-      <c r="B11" s="14" t="n"/>
-      <c r="C11" s="14" t="n"/>
-      <c r="D11" s="14" t="n"/>
-      <c r="E11" s="14" t="n"/>
-      <c r="F11" s="15" t="n"/>
+      <c r="A11" s="20" t="inlineStr">
+        <is>
+          <t>二、语义模型（L3报表.SemanticModel）</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="20" t="inlineStr">
-        <is>
-          <t>二、语义模型（L3报表.SemanticModel）</t>
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>语义模型定义版本：4.2　｜　兼容级别：1702</t>
         </is>
       </c>
     </row>
     <row r="13" ht="19.95" customHeight="1" s="17">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>语义模型定义版本：4.2　｜　兼容级别：1702</t>
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>事实表 KFM选冶厂月报（19 列）</t>
         </is>
       </c>
     </row>
     <row r="14" ht="19.95" customHeight="1" s="17">
-      <c r="A14" s="16" t="inlineStr">
-        <is>
-          <t>事实表 KFM选冶厂月报（19 列）</t>
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>累计实际数</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="inlineStr">
+        <is>
+          <t>累计预测数</t>
+        </is>
+      </c>
+      <c r="E14" s="1" t="inlineStr">
+        <is>
+          <t>累计预算数</t>
         </is>
       </c>
     </row>
     <row r="15" ht="19.95" customHeight="1" s="17">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>累计实际数</t>
+          <t>实际数</t>
         </is>
       </c>
       <c r="C15" s="1" t="inlineStr">
         <is>
-          <t>累计预测数</t>
+          <t>预测数</t>
         </is>
       </c>
       <c r="E15" s="1" t="inlineStr">
         <is>
-          <t>累计预算数</t>
+          <t>预算数</t>
         </is>
       </c>
     </row>
     <row r="16" ht="19.95" customHeight="1" s="17">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>实际数</t>
+          <t>月份</t>
         </is>
       </c>
       <c r="C16" s="1" t="inlineStr">
         <is>
-          <t>预测数</t>
+          <t>指标项</t>
         </is>
       </c>
       <c r="E16" s="1" t="inlineStr">
         <is>
-          <t>预算数</t>
+          <t>序号</t>
         </is>
       </c>
     </row>
     <row r="17" ht="19.95" customHeight="1" s="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>月份</t>
+          <t>总类别</t>
         </is>
       </c>
       <c r="C17" s="1" t="inlineStr">
         <is>
-          <t>指标项</t>
+          <t>二级指标</t>
         </is>
       </c>
       <c r="E17" s="1" t="inlineStr">
         <is>
-          <t>序号</t>
+          <t>日期</t>
         </is>
       </c>
     </row>
     <row r="18" ht="19.95" customHeight="1" s="17">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>总类别</t>
+          <t>环节序号</t>
         </is>
       </c>
       <c r="C18" s="1" t="inlineStr">
         <is>
-          <t>类别2</t>
+          <t>月份-筛选器</t>
         </is>
       </c>
       <c r="E18" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>排序</t>
         </is>
       </c>
     </row>
     <row r="19" ht="19.95" customHeight="1" s="17">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>环节序号</t>
+          <t>产品分类</t>
         </is>
       </c>
       <c r="C19" s="1" t="inlineStr">
         <is>
-          <t>月份-筛选器</t>
+          <t>单位</t>
         </is>
       </c>
       <c r="E19" s="1" t="inlineStr">
         <is>
-          <t>排序</t>
+          <t>全年预算数</t>
         </is>
       </c>
     </row>
     <row r="20" ht="19.95" customHeight="1" s="17">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>产品分类</t>
-        </is>
-      </c>
-      <c r="C20" s="1" t="inlineStr">
+          <t>指标类别</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="19.95" customHeight="1" s="17">
+      <c r="A21" s="16" t="inlineStr">
+        <is>
+          <t>事实表 L1-KFM日报（17 列）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="19.95" customHeight="1" s="17">
+      <c r="A22" s="1" t="inlineStr">
         <is>
           <t>单位</t>
         </is>
       </c>
-      <c r="E20" s="1" t="inlineStr">
-        <is>
-          <t>全年预算数</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="19.95" customHeight="1" s="17">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>指标类别</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="19.95" customHeight="1" s="17">
-      <c r="A22" s="16" t="inlineStr">
-        <is>
-          <t>事实表 L1-KFM日报（17 列）</t>
+      <c r="C22" s="1" t="inlineStr">
+        <is>
+          <t>当日实际数</t>
+        </is>
+      </c>
+      <c r="E22" s="1" t="inlineStr">
+        <is>
+          <t>当月累计实际数</t>
         </is>
       </c>
     </row>
     <row r="23" ht="19.95" customHeight="1" s="17">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>单位</t>
+          <t>地域</t>
         </is>
       </c>
       <c r="C23" s="1" t="inlineStr">
         <is>
-          <t>当日实际数</t>
+          <t>序号</t>
         </is>
       </c>
       <c r="E23" s="1" t="inlineStr">
         <is>
-          <t>当月累计实际数</t>
+          <t>二级指标</t>
         </is>
       </c>
     </row>
     <row r="24" ht="19.95" customHeight="1" s="17">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>地域</t>
+          <t>排序</t>
         </is>
       </c>
       <c r="C24" s="1" t="inlineStr">
         <is>
-          <t>序号</t>
+          <t>总类别</t>
         </is>
       </c>
       <c r="E24" s="1" t="inlineStr">
         <is>
-          <t>类别2</t>
+          <t>环节序号</t>
         </is>
       </c>
     </row>
     <row r="25" ht="19.95" customHeight="1" s="17">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>排序</t>
+          <t>全年预算数</t>
         </is>
       </c>
       <c r="C25" s="1" t="inlineStr">
         <is>
-          <t>总类别</t>
+          <t>月计划</t>
         </is>
       </c>
       <c r="E25" s="1" t="inlineStr">
         <is>
-          <t>环节序号</t>
+          <t>月预算</t>
         </is>
       </c>
     </row>
     <row r="26" ht="19.95" customHeight="1" s="17">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>全年预算数</t>
+          <t>标准日期</t>
         </is>
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
-          <t>月计划</t>
+          <t>累计实际数</t>
         </is>
       </c>
       <c r="E26" s="1" t="inlineStr">
         <is>
-          <t>月预算</t>
+          <t>日期筛选器</t>
         </is>
       </c>
     </row>
     <row r="27" ht="19.95" customHeight="1" s="17">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>标准日期</t>
+          <t>产品分类</t>
         </is>
       </c>
       <c r="C27" s="1" t="inlineStr">
         <is>
-          <t>累计实际数</t>
-        </is>
-      </c>
-      <c r="E27" s="1" t="inlineStr">
-        <is>
-          <t>日期筛选器</t>
-        </is>
-      </c>
+          <t>指标名称</t>
+        </is>
+      </c>
+      <c r="E27" s="1" t="n"/>
     </row>
     <row r="28" ht="19.95" customHeight="1" s="17">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>产品分类</t>
-        </is>
-      </c>
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t>指标名称</t>
-        </is>
-      </c>
+      <c r="A28" s="1" t="n"/>
+      <c r="C28" s="1" t="n"/>
       <c r="E28" s="1" t="n"/>
     </row>
     <row r="29" ht="19.95" customHeight="1" s="17">
@@ -1107,60 +1096,67 @@
       <c r="E31" s="1" t="n"/>
     </row>
     <row r="32" ht="14.7" customHeight="1" s="17">
-      <c r="A32" s="1" t="n"/>
-      <c r="C32" s="1" t="n"/>
-      <c r="E32" s="1" t="n"/>
+      <c r="A32" s="16" t="inlineStr">
+        <is>
+          <t>映射表（各 6 列）：日报指标映射、月报指标映射</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="22.05" customHeight="1" s="17">
-      <c r="A33" s="16" t="inlineStr">
-        <is>
-          <t>映射表（各 6 列）：日报指标映射、月报指标映射</t>
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>指标项</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>类别</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>环节</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>环节序号</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>报表</t>
         </is>
       </c>
     </row>
     <row r="34" ht="34.95" customHeight="1" s="17">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>序号</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>指标项</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>类别</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>环节</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>环节序号</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>报表</t>
+      <c r="A34" s="16" t="inlineStr">
+        <is>
+          <t>度量值表（28 个度量值）</t>
         </is>
       </c>
     </row>
     <row r="35" ht="19.5" customHeight="1" s="17">
-      <c r="A35" s="16" t="inlineStr">
-        <is>
-          <t>度量值表（34 个度量值）</t>
-        </is>
-      </c>
+      <c r="A35" s="21" t="inlineStr">
+        <is>
+          <t>月报度量（9 个）：月计划、月完成、月比计划、月计划累计、年累计完成、年比计划、同期年累计完成、年计划、年累计完成比计划</t>
+        </is>
+      </c>
+      <c r="B35" s="14" t="n"/>
+      <c r="C35" s="14" t="n"/>
+      <c r="D35" s="14" t="n"/>
+      <c r="E35" s="14" t="n"/>
+      <c r="F35" s="15" t="n"/>
     </row>
     <row r="36" ht="19.5" customHeight="1" s="17">
-      <c r="A36" s="21" t="inlineStr">
-        <is>
-          <t>月报度量（9 个）：月计划、月完成、月比计划、月计划累计、年累计完成、年比计划、同期年累计完成、年计划、年累计完成比计划</t>
+      <c r="A36" s="23" t="inlineStr">
+        <is>
+          <t>日报度量（8 个）：日完成、月累计、月计划L1、月比计划L1、年计划L1、年累计完成L1、年比计划L1、年累计完成L1_v2</t>
         </is>
       </c>
       <c r="B36" s="14" t="n"/>
@@ -1172,7 +1168,7 @@
     <row r="37" ht="22.05" customHeight="1" s="17">
       <c r="A37" s="23" t="inlineStr">
         <is>
-          <t>日报度量（8 个）：日完成、月累计、月计划L1、月比计划L1、年计划L1、年累计完成L1、年比计划L1、年累计完成L1_v2</t>
+          <t>入选品位度量（4 个）：v钴入矿品位_新口径、v铜入矿品位_新口径、v铜回收率_新口径、v_钴回收率_新口径</t>
         </is>
       </c>
       <c r="B37" s="14" t="n"/>
@@ -1182,9 +1178,9 @@
       <c r="F37" s="15" t="n"/>
     </row>
     <row r="38" ht="40" customHeight="1" s="17">
-      <c r="A38" s="23" t="inlineStr">
-        <is>
-          <t>入选品位度量（10 个）：日累计全钴TCo入磨金属量、日累计全铜TCu入磨金属量、日累计原矿处理量、月累计全钴TCo入磨金属量、月累计全铜TCu入磨金属量、月累计原矿处理量、年累计全钴TCo入矿品位、年累计全铜TCu入矿品位、v年累计全钴TCo入矿品位、v年累计全铜TCu入矿品位</t>
+      <c r="A38" s="21" t="inlineStr">
+        <is>
+          <t>辅助/标题（7 个）：.（占位）、标题-月报、标题-月份、标题-年累计、标题-年全年、标题-同期年、标题-日报</t>
         </is>
       </c>
       <c r="B38" s="14" t="n"/>
@@ -1194,28 +1190,28 @@
       <c r="F38" s="15" t="n"/>
     </row>
     <row r="39" ht="19.5" customHeight="1" s="17">
-      <c r="A39" s="21" t="inlineStr">
-        <is>
-          <t>辅助/标题（7 个）：.（占位）、标题-月报、标题-月份、标题-年累计、标题-年全年、标题-同期年、标题-日报</t>
-        </is>
-      </c>
-      <c r="B39" s="14" t="n"/>
-      <c r="C39" s="14" t="n"/>
-      <c r="D39" s="14" t="n"/>
-      <c r="E39" s="14" t="n"/>
-      <c r="F39" s="15" t="n"/>
+      <c r="A39" s="16" t="inlineStr">
+        <is>
+          <t>DAX 函数（functions.tmdl，3 个）：FormatAmount（数量格式）、FormatRatio（比率格式）、SameMonthPriorYear（去年同月）</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="16" t="inlineStr">
-        <is>
-          <t>DAX 函数（functions.tmdl，3 个）：FormatAmount（数量格式）、FormatRatio（比率格式）、SameMonthPriorYear（去年同月）</t>
-        </is>
-      </c>
+      <c r="A40" s="21" t="inlineStr">
+        <is>
+          <t>Power Query 参数：p_月报起始日期=2025-01-01、p_日报起始日期=2026-01-01、服务器/系统编号/客户端ID/SharePoint站点（中间表 全年预算表、月累计实际表 已内联进 L1-KFM日报）</t>
+        </is>
+      </c>
+      <c r="B40" s="14" t="n"/>
+      <c r="C40" s="14" t="n"/>
+      <c r="D40" s="14" t="n"/>
+      <c r="E40" s="14" t="n"/>
+      <c r="F40" s="15" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="21" t="inlineStr">
-        <is>
-          <t>Power Query 参数：p_月报起始日期=2025-01-01、p_日报起始日期=2026-01-01、服务器/系统编号/客户端ID/SharePoint站点（中间表 全年预算表、月累计实际表 已内联进 L1-KFM日报）</t>
+      <c r="A41" s="25" t="inlineStr">
+        <is>
+          <t>说明：原「指标映射」表已拆分为日报/月报两张映射表；relationships.tmdl 已删除（关系随映射表拆分调整）。</t>
         </is>
       </c>
       <c r="B41" s="14" t="n"/>
@@ -1224,18 +1220,7 @@
       <c r="E41" s="14" t="n"/>
       <c r="F41" s="15" t="n"/>
     </row>
-    <row r="42">
-      <c r="A42" s="25" t="inlineStr">
-        <is>
-          <t>说明：原「指标映射」表已拆分为日报/月报两张映射表；relationships.tmdl 已删除（关系随映射表拆分调整）。</t>
-        </is>
-      </c>
-      <c r="B42" s="14" t="n"/>
-      <c r="C42" s="14" t="n"/>
-      <c r="D42" s="14" t="n"/>
-      <c r="E42" s="14" t="n"/>
-      <c r="F42" s="15" t="n"/>
-    </row>
+    <row r="42"/>
   </sheetData>
   <mergeCells count="30">
     <mergeCell ref="A41:F41"/>
@@ -1279,7 +1264,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="5" customWidth="1" style="17" min="1" max="1"/>
@@ -1352,52 +1337,52 @@
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" s="17">
-      <c r="A2" s="13" t="n">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="13" t="inlineStr">
-        <is>
-          <t>6e604e4</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>6e604e4d0315cd3426b5f37097aed19041b27654</t>
-        </is>
-      </c>
-      <c r="D2" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-14 18:41:35</t>
-        </is>
-      </c>
-      <c r="E2" s="13" t="inlineStr">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>03b7f44</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>03b7f44d157dc79e23a7b3cd8c6f93bbdc3b36a4</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-10-15 10:05:16</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>Jevon Zhu</t>
         </is>
       </c>
-      <c r="F2" s="13" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>jevonzhu2008@gmail.com</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>日报表新增入选品位度量值与指标列，同步月报口径、报表页面与分析报告</t>
-        </is>
-      </c>
-      <c r="H2" s="13" t="inlineStr">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>二级指标列改名与入选品位/回收率新口径，同步报表与分析报告</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="I2" s="13" t="n">
-        <v>18</v>
-      </c>
-      <c r="J2" s="13" t="n">
-        <v>1565</v>
-      </c>
-      <c r="K2" s="13" t="n">
-        <v>175</v>
+      <c r="I2" t="n">
+        <v>34</v>
+      </c>
+      <c r="J2" t="n">
+        <v>348</v>
+      </c>
+      <c r="K2" t="n">
+        <v>10809</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" s="17">
@@ -1406,17 +1391,17 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>d6b1785</t>
+          <t>6e604e4</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>d6b1785b86f19f2db61866bfc840abcac3e1f2cf</t>
+          <t>6e604e4d0315cd3426b5f37097aed19041b27654</t>
         </is>
       </c>
       <c r="D3" s="13" t="inlineStr">
         <is>
-          <t>2026-10-14 14:05:13</t>
+          <t>2026-10-14 18:41:35</t>
         </is>
       </c>
       <c r="E3" s="13" t="inlineStr">
@@ -1431,7 +1416,7 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>重命名报表项目：L3报表-KFM日月报 → L3报表</t>
+          <t>日报表新增入选品位度量值与指标列，同步月报口径、报表页面与分析报告</t>
         </is>
       </c>
       <c r="H3" s="13" t="inlineStr">
@@ -1440,13 +1425,13 @@
         </is>
       </c>
       <c r="I3" s="13" t="n">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="J3" s="13" t="n">
-        <v>23</v>
+        <v>1565</v>
       </c>
       <c r="K3" s="13" t="n">
-        <v>17</v>
+        <v>175</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" s="17">
@@ -1455,879 +1440,928 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
+          <t>d6b1785</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>d6b1785b86f19f2db61866bfc840abcac3e1f2cf</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-14 14:05:13</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>重命名报表项目：L3报表-KFM日月报 → L3报表</t>
+        </is>
+      </c>
+      <c r="H4" s="13" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I4" s="13" t="n">
+        <v>68</v>
+      </c>
+      <c r="J4" s="13" t="n">
+        <v>23</v>
+      </c>
+      <c r="K4" s="13" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1" s="17">
+      <c r="A5" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
           <t>8c90e31</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>8c90e3154248a749ec3ef3bc61d68576b709d2f7</t>
         </is>
       </c>
-      <c r="D4" s="13" t="inlineStr">
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t>2026-10-14 12:08:57</t>
         </is>
       </c>
-      <c r="E4" s="13" t="inlineStr">
+      <c r="E5" s="13" t="inlineStr">
         <is>
           <t>Jevon Zhu</t>
         </is>
       </c>
-      <c r="F4" s="13" t="inlineStr">
+      <c r="F5" s="13" t="inlineStr">
         <is>
           <t>jevonzhu2008@gmail.com</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>更新语义模型分析报告：同步 M 优化与列精简</t>
         </is>
       </c>
-      <c r="H4" s="13" t="inlineStr">
+      <c r="H5" s="13" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="I4" s="13" t="n">
+      <c r="I5" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="J4" s="13" t="n">
+      <c r="J5" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="K4" s="13" t="n">
+      <c r="K5" s="13" t="n">
         <v>16</v>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1" s="17">
-      <c r="A5" s="18" t="n">
+    <row r="6" ht="30" customHeight="1" s="17">
+      <c r="A6" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t>7148b64</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>7148b64ddd4ee32a7c06e2f912d939dc2ba4e1b5</t>
+        </is>
+      </c>
+      <c r="D6" s="18" t="inlineStr">
+        <is>
+          <t>2026-10-14 11:35:22</t>
+        </is>
+      </c>
+      <c r="E6" s="18" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F6" s="18" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>优化语义模型 M 代码与输出列</t>
+        </is>
+      </c>
+      <c r="H6" s="18" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I6" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="J6" s="18" t="n">
+        <v>38</v>
+      </c>
+      <c r="K6" s="18" t="n">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1" s="17">
+      <c r="A7" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>f996ae9</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>f996ae982e67b13a495117c8a9b34531f4eded82</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-14 11:35:16</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>调整报告页面命名与日报日期筛选</t>
+        </is>
+      </c>
+      <c r="H7" s="13" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I7" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="J7" s="13" t="n">
+        <v>133</v>
+      </c>
+      <c r="K7" s="13" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1" s="17">
+      <c r="A8" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>630c17f</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>630c17fceaf47b46c21633e044fda78155ac0443</t>
+        </is>
+      </c>
+      <c r="D8" s="18" t="inlineStr">
+        <is>
+          <t>2026-10-14 10:06:29</t>
+        </is>
+      </c>
+      <c r="E8" s="18" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F8" s="18" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>更新语义模型分析报告：同步本轮修复</t>
+        </is>
+      </c>
+      <c r="H8" s="18" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I8" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="18" t="n">
+        <v>35</v>
+      </c>
+      <c r="K8" s="18" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1" s="17">
+      <c r="A9" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>1794160</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>179416093e3aff5472f3a2f4719d2270cff850d1</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-14 10:06:24</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>调整报告视觉对象布局与筛选</t>
+        </is>
+      </c>
+      <c r="H9" s="13" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I9" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="J9" s="13" t="n">
+        <v>37</v>
+      </c>
+      <c r="K9" s="13" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1" s="17">
+      <c r="A10" s="18" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="18" t="inlineStr">
+        <is>
+          <t>9cbf408</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>9cbf408d9186e1be6583b91b3e445288720dab30</t>
+        </is>
+      </c>
+      <c r="D10" s="18" t="inlineStr">
+        <is>
+          <t>2026-10-14 10:06:18</t>
+        </is>
+      </c>
+      <c r="E10" s="18" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F10" s="18" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>修复语义模型分析报告发现的问题</t>
+        </is>
+      </c>
+      <c r="H10" s="18" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I10" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="J10" s="18" t="n">
+        <v>86</v>
+      </c>
+      <c r="K10" s="18" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1" s="17">
+      <c r="A11" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>07f180b</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>07f180b9740c0c72f4ff4cb637acce0c8b718efc</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-14 07:21:58</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F11" s="13" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>修正日报度量值：清理标题围栏并调整年累计完成字段</t>
+        </is>
+      </c>
+      <c r="H11" s="13" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I11" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="K11" s="13" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1" s="17">
+      <c r="A12" s="18" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="18" t="inlineStr">
+        <is>
+          <t>2d4f16f</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>2d4f16fda737382909dd93ca2b175b6618fcbb57</t>
+        </is>
+      </c>
+      <c r="D12" s="18" t="inlineStr">
+        <is>
+          <t>2026-10-14 07:01:02</t>
+        </is>
+      </c>
+      <c r="E12" s="18" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F12" s="18" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>新增 KFM日月报语义模型分析报告</t>
+        </is>
+      </c>
+      <c r="H12" s="18" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I12" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="18" t="n">
+        <v>320</v>
+      </c>
+      <c r="K12" s="18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1" s="17">
+      <c r="A13" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>5ba71b7</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>5ba71b7bdd8c9fa3140791e2c325425796229e13</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-14 06:57:45</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>修正 DAX/M 代码注释，准确反映实际逻辑</t>
+        </is>
+      </c>
+      <c r="H13" s="13" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I13" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="J13" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="K13" s="13" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1" s="17">
+      <c r="A14" s="18" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="18" t="inlineStr">
+        <is>
+          <t>cea3882</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>cea3882903b1e0ebd284ee0a2acadb18380ddd7f</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="inlineStr">
+        <is>
+          <t>2026-10-14 06:34:36</t>
+        </is>
+      </c>
+      <c r="E14" s="18" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F14" s="18" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>优化语义模型自定义函数命名</t>
+        </is>
+      </c>
+      <c r="H14" s="18" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I14" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="J14" s="18" t="n">
+        <v>17</v>
+      </c>
+      <c r="K14" s="18" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1" s="17">
+      <c r="A15" s="13" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>9f32794</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>9f32794cc45bd00e695f720d0e38ca7eda0ee97d</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-14 06:22:46</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F15" s="13" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>重命名报表项目：KFM选冶厂月报 → L3报表-KFM日月报</t>
+        </is>
+      </c>
+      <c r="H15" s="13" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I15" s="13" t="n">
+        <v>70</v>
+      </c>
+      <c r="J15" s="13" t="n">
+        <v>695</v>
+      </c>
+      <c r="K15" s="13" t="n">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1" s="17">
+      <c r="A16" s="18" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="18" t="inlineStr">
+        <is>
+          <t>07301c6</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>07301c63639499dc1642f9abe29a9baee1e0c3cf</t>
+        </is>
+      </c>
+      <c r="D16" s="18" t="inlineStr">
+        <is>
+          <t>2026-10-13 19:57:45</t>
+        </is>
+      </c>
+      <c r="E16" s="18" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F16" s="18" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>修复 KFM选冶厂月报 TMDL 缩进错误</t>
+        </is>
+      </c>
+      <c r="H16" s="18" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I16" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1" s="17">
+      <c r="A17" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>1485d55</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>1485d55c4d5b2c241eb05e9040a3897476085331</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-13 19:45:55</t>
+        </is>
+      </c>
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F17" s="13" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>优化全部 M 查询：步骤名语义化与步骤合并</t>
+        </is>
+      </c>
+      <c r="H17" s="13" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I17" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="18" t="inlineStr">
-        <is>
-          <t>7148b64</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>7148b64ddd4ee32a7c06e2f912d939dc2ba4e1b5</t>
-        </is>
-      </c>
-      <c r="D5" s="18" t="inlineStr">
-        <is>
-          <t>2026-10-14 11:35:22</t>
-        </is>
-      </c>
-      <c r="E5" s="18" t="inlineStr">
+      <c r="J17" s="13" t="n">
+        <v>134</v>
+      </c>
+      <c r="K17" s="13" t="n">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1" s="17">
+      <c r="A18" s="18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="18" t="inlineStr">
+        <is>
+          <t>6b4084c</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>6b4084c9a3fb078c53fcbdd2549a2adc1fc7d100</t>
+        </is>
+      </c>
+      <c r="D18" s="18" t="inlineStr">
+        <is>
+          <t>2026-10-13 19:31:50</t>
+        </is>
+      </c>
+      <c r="E18" s="18" t="inlineStr">
         <is>
           <t>Jevon Zhu</t>
         </is>
       </c>
-      <c r="F5" s="18" t="inlineStr">
+      <c r="F18" s="18" t="inlineStr">
         <is>
           <t>jevonzhu2008@gmail.com</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>优化语义模型 M 代码与输出列</t>
-        </is>
-      </c>
-      <c r="H5" s="18" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>优化L1-KFM日报 M 查询：命名注释与步骤精简</t>
+        </is>
+      </c>
+      <c r="H18" s="18" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="I5" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="J5" s="18" t="n">
-        <v>38</v>
-      </c>
-      <c r="K5" s="18" t="n">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1" s="17">
-      <c r="A6" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>f996ae9</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>f996ae982e67b13a495117c8a9b34531f4eded82</t>
-        </is>
-      </c>
-      <c r="D6" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-14 11:35:16</t>
-        </is>
-      </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="I18" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" s="18" t="n">
+        <v>130</v>
+      </c>
+      <c r="K18" s="18" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1" s="17">
+      <c r="A19" s="13" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>2a59e2f</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>2a59e2f68de3a82d02c6493c75d4a170ce013fae</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-13 19:15:18</t>
+        </is>
+      </c>
+      <c r="E19" s="13" t="inlineStr">
         <is>
           <t>Jevon Zhu</t>
         </is>
       </c>
-      <c r="F6" s="13" t="inlineStr">
+      <c r="F19" s="13" t="inlineStr">
         <is>
           <t>jevonzhu2008@gmail.com</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>调整报告页面命名与日报日期筛选</t>
-        </is>
-      </c>
-      <c r="H6" s="13" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>优化L1-KFM日报 M 查询：内联两个中间表</t>
+        </is>
+      </c>
+      <c r="H19" s="13" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="I6" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="J6" s="13" t="n">
-        <v>133</v>
-      </c>
-      <c r="K6" s="13" t="n">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1" s="17">
-      <c r="A7" s="18" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>630c17f</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>630c17fceaf47b46c21633e044fda78155ac0443</t>
-        </is>
-      </c>
-      <c r="D7" s="18" t="inlineStr">
-        <is>
-          <t>2026-10-14 10:06:29</t>
-        </is>
-      </c>
-      <c r="E7" s="18" t="inlineStr">
+      <c r="I19" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="J19" s="13" t="n">
+        <v>21</v>
+      </c>
+      <c r="K19" s="13" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1" s="17">
+      <c r="A20" s="18" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="18" t="inlineStr">
+        <is>
+          <t>48112a2</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>48112a2bfe1b2809ef94fe779a2e7a6c65d60bb2</t>
+        </is>
+      </c>
+      <c r="D20" s="18" t="inlineStr">
+        <is>
+          <t>2026-10-13 18:55:27</t>
+        </is>
+      </c>
+      <c r="E20" s="18" t="inlineStr">
         <is>
           <t>Jevon Zhu</t>
         </is>
       </c>
-      <c r="F7" s="18" t="inlineStr">
+      <c r="F20" s="18" t="inlineStr">
         <is>
           <t>jevonzhu2008@gmail.com</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>更新语义模型分析报告：同步本轮修复</t>
-        </is>
-      </c>
-      <c r="H7" s="18" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>升级语义模型兼容级别1702，新增日报模型与DAX函数(UDF)</t>
+        </is>
+      </c>
+      <c r="H20" s="18" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="I7" s="18" t="n">
+      <c r="I20" s="18" t="n">
+        <v>35</v>
+      </c>
+      <c r="J20" s="18" t="n">
+        <v>5662</v>
+      </c>
+      <c r="K20" s="18" t="n">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>69bb2ba</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>69bb2ba9dc7aa839a00235f2ef0ed1b691d7384e</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-13 01:42:09</t>
+        </is>
+      </c>
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F21" s="13" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>新增项目版本信息 Excel 文档（含项目概述、Git版本历史、提交备注）</t>
+        </is>
+      </c>
+      <c r="H21" s="13" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I21" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="J7" s="18" t="n">
-        <v>35</v>
-      </c>
-      <c r="K7" s="18" t="n">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1" s="17">
-      <c r="A8" s="13" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>1794160</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>179416093e3aff5472f3a2f4719d2270cff850d1</t>
-        </is>
-      </c>
-      <c r="D8" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-14 10:06:24</t>
-        </is>
-      </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="J21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="18" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="18" t="inlineStr">
+        <is>
+          <t>248840e</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>248840e9d232eacba69832ed5401065fb3ce1cab</t>
+        </is>
+      </c>
+      <c r="D22" s="18" t="inlineStr">
+        <is>
+          <t>2026-10-13 01:07:27</t>
+        </is>
+      </c>
+      <c r="E22" s="18" t="inlineStr">
         <is>
           <t>Jevon Zhu</t>
         </is>
       </c>
-      <c r="F8" s="13" t="inlineStr">
+      <c r="F22" s="18" t="inlineStr">
         <is>
           <t>jevonzhu2008@gmail.com</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>调整报告视觉对象布局与筛选</t>
-        </is>
-      </c>
-      <c r="H8" s="13" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>初始化存档：KFM选冶厂月报 Power BI 项目（PBIP）</t>
+        </is>
+      </c>
+      <c r="H22" s="18" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="I8" s="13" t="n">
-        <v>7</v>
-      </c>
-      <c r="J8" s="13" t="n">
-        <v>37</v>
-      </c>
-      <c r="K8" s="13" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1" s="17">
-      <c r="A9" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>9cbf408</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>9cbf408d9186e1be6583b91b3e445288720dab30</t>
-        </is>
-      </c>
-      <c r="D9" s="18" t="inlineStr">
-        <is>
-          <t>2026-10-14 10:06:18</t>
-        </is>
-      </c>
-      <c r="E9" s="18" t="inlineStr">
-        <is>
-          <t>Jevon Zhu</t>
-        </is>
-      </c>
-      <c r="F9" s="18" t="inlineStr">
-        <is>
-          <t>jevonzhu2008@gmail.com</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>修复语义模型分析报告发现的问题</t>
-        </is>
-      </c>
-      <c r="H9" s="18" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="I9" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="J9" s="18" t="n">
-        <v>86</v>
-      </c>
-      <c r="K9" s="18" t="n">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1" s="17">
-      <c r="A10" s="13" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>07f180b</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>07f180b9740c0c72f4ff4cb637acce0c8b718efc</t>
-        </is>
-      </c>
-      <c r="D10" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-14 07:21:58</t>
-        </is>
-      </c>
-      <c r="E10" s="13" t="inlineStr">
-        <is>
-          <t>Jevon Zhu</t>
-        </is>
-      </c>
-      <c r="F10" s="13" t="inlineStr">
-        <is>
-          <t>jevonzhu2008@gmail.com</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>修正日报度量值：清理标题围栏并调整年累计完成字段</t>
-        </is>
-      </c>
-      <c r="H10" s="13" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="I10" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="K10" s="13" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1" s="17">
-      <c r="A11" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>2d4f16f</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>2d4f16fda737382909dd93ca2b175b6618fcbb57</t>
-        </is>
-      </c>
-      <c r="D11" s="18" t="inlineStr">
-        <is>
-          <t>2026-10-14 07:01:02</t>
-        </is>
-      </c>
-      <c r="E11" s="18" t="inlineStr">
-        <is>
-          <t>Jevon Zhu</t>
-        </is>
-      </c>
-      <c r="F11" s="18" t="inlineStr">
-        <is>
-          <t>jevonzhu2008@gmail.com</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>新增 KFM日月报语义模型分析报告</t>
-        </is>
-      </c>
-      <c r="H11" s="18" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="I11" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" s="18" t="n">
-        <v>320</v>
-      </c>
-      <c r="K11" s="18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1" s="17">
-      <c r="A12" s="13" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="13" t="inlineStr">
-        <is>
-          <t>5ba71b7</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>5ba71b7bdd8c9fa3140791e2c325425796229e13</t>
-        </is>
-      </c>
-      <c r="D12" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-14 06:57:45</t>
-        </is>
-      </c>
-      <c r="E12" s="13" t="inlineStr">
-        <is>
-          <t>Jevon Zhu</t>
-        </is>
-      </c>
-      <c r="F12" s="13" t="inlineStr">
-        <is>
-          <t>jevonzhu2008@gmail.com</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>修正 DAX/M 代码注释，准确反映实际逻辑</t>
-        </is>
-      </c>
-      <c r="H12" s="13" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="I12" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="J12" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="K12" s="13" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1" s="17">
-      <c r="A13" s="18" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>cea3882</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>cea3882903b1e0ebd284ee0a2acadb18380ddd7f</t>
-        </is>
-      </c>
-      <c r="D13" s="18" t="inlineStr">
-        <is>
-          <t>2026-10-14 06:34:36</t>
-        </is>
-      </c>
-      <c r="E13" s="18" t="inlineStr">
-        <is>
-          <t>Jevon Zhu</t>
-        </is>
-      </c>
-      <c r="F13" s="18" t="inlineStr">
-        <is>
-          <t>jevonzhu2008@gmail.com</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>优化语义模型自定义函数命名</t>
-        </is>
-      </c>
-      <c r="H13" s="18" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="I13" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="J13" s="18" t="n">
-        <v>17</v>
-      </c>
-      <c r="K13" s="18" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1" s="17">
-      <c r="A14" s="13" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="13" t="inlineStr">
-        <is>
-          <t>9f32794</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>9f32794cc45bd00e695f720d0e38ca7eda0ee97d</t>
-        </is>
-      </c>
-      <c r="D14" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-14 06:22:46</t>
-        </is>
-      </c>
-      <c r="E14" s="13" t="inlineStr">
-        <is>
-          <t>Jevon Zhu</t>
-        </is>
-      </c>
-      <c r="F14" s="13" t="inlineStr">
-        <is>
-          <t>jevonzhu2008@gmail.com</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>重命名报表项目：KFM选冶厂月报 → L3报表-KFM日月报</t>
-        </is>
-      </c>
-      <c r="H14" s="13" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="I14" s="13" t="n">
-        <v>70</v>
-      </c>
-      <c r="J14" s="13" t="n">
-        <v>695</v>
-      </c>
-      <c r="K14" s="13" t="n">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1" s="17">
-      <c r="A15" s="18" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>07301c6</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>07301c63639499dc1642f9abe29a9baee1e0c3cf</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>2026-10-13 19:57:45</t>
-        </is>
-      </c>
-      <c r="E15" s="18" t="inlineStr">
-        <is>
-          <t>Jevon Zhu</t>
-        </is>
-      </c>
-      <c r="F15" s="18" t="inlineStr">
-        <is>
-          <t>jevonzhu2008@gmail.com</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>修复 KFM选冶厂月报 TMDL 缩进错误</t>
-        </is>
-      </c>
-      <c r="H15" s="18" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="I15" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="J15" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="K15" s="18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1" s="17">
-      <c r="A16" s="13" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="13" t="inlineStr">
-        <is>
-          <t>1485d55</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>1485d55c4d5b2c241eb05e9040a3897476085331</t>
-        </is>
-      </c>
-      <c r="D16" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-13 19:45:55</t>
-        </is>
-      </c>
-      <c r="E16" s="13" t="inlineStr">
-        <is>
-          <t>Jevon Zhu</t>
-        </is>
-      </c>
-      <c r="F16" s="13" t="inlineStr">
-        <is>
-          <t>jevonzhu2008@gmail.com</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>优化全部 M 查询：步骤名语义化与步骤合并</t>
-        </is>
-      </c>
-      <c r="H16" s="13" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="I16" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="J16" s="13" t="n">
-        <v>134</v>
-      </c>
-      <c r="K16" s="13" t="n">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1" s="17">
-      <c r="A17" s="18" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>6b4084c</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>6b4084c9a3fb078c53fcbdd2549a2adc1fc7d100</t>
-        </is>
-      </c>
-      <c r="D17" s="18" t="inlineStr">
-        <is>
-          <t>2026-10-13 19:31:50</t>
-        </is>
-      </c>
-      <c r="E17" s="18" t="inlineStr">
-        <is>
-          <t>Jevon Zhu</t>
-        </is>
-      </c>
-      <c r="F17" s="18" t="inlineStr">
-        <is>
-          <t>jevonzhu2008@gmail.com</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>优化L1-KFM日报 M 查询：命名注释与步骤精简</t>
-        </is>
-      </c>
-      <c r="H17" s="18" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="I17" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" s="18" t="n">
-        <v>130</v>
-      </c>
-      <c r="K17" s="18" t="n">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1" s="17">
-      <c r="A18" s="13" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="13" t="inlineStr">
-        <is>
-          <t>2a59e2f</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>2a59e2f68de3a82d02c6493c75d4a170ce013fae</t>
-        </is>
-      </c>
-      <c r="D18" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-13 19:15:18</t>
-        </is>
-      </c>
-      <c r="E18" s="13" t="inlineStr">
-        <is>
-          <t>Jevon Zhu</t>
-        </is>
-      </c>
-      <c r="F18" s="13" t="inlineStr">
-        <is>
-          <t>jevonzhu2008@gmail.com</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>优化L1-KFM日报 M 查询：内联两个中间表</t>
-        </is>
-      </c>
-      <c r="H18" s="13" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="I18" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="J18" s="13" t="n">
-        <v>21</v>
-      </c>
-      <c r="K18" s="13" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1" s="17">
-      <c r="A19" s="18" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>48112a2</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>48112a2bfe1b2809ef94fe779a2e7a6c65d60bb2</t>
-        </is>
-      </c>
-      <c r="D19" s="18" t="inlineStr">
-        <is>
-          <t>2026-10-13 18:55:27</t>
-        </is>
-      </c>
-      <c r="E19" s="18" t="inlineStr">
-        <is>
-          <t>Jevon Zhu</t>
-        </is>
-      </c>
-      <c r="F19" s="18" t="inlineStr">
-        <is>
-          <t>jevonzhu2008@gmail.com</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>升级语义模型兼容级别1702，新增日报模型与DAX函数(UDF)</t>
-        </is>
-      </c>
-      <c r="H19" s="18" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="I19" s="18" t="n">
-        <v>35</v>
-      </c>
-      <c r="J19" s="18" t="n">
-        <v>5662</v>
-      </c>
-      <c r="K19" s="18" t="n">
-        <v>771</v>
-      </c>
-    </row>
-    <row r="20" ht="30" customHeight="1" s="17">
-      <c r="A20" s="13" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="13" t="inlineStr">
-        <is>
-          <t>69bb2ba</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>69bb2ba9dc7aa839a00235f2ef0ed1b691d7384e</t>
-        </is>
-      </c>
-      <c r="D20" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-13 01:42:09</t>
-        </is>
-      </c>
-      <c r="E20" s="13" t="inlineStr">
-        <is>
-          <t>Jevon Zhu</t>
-        </is>
-      </c>
-      <c r="F20" s="13" t="inlineStr">
-        <is>
-          <t>jevonzhu2008@gmail.com</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>新增项目版本信息 Excel 文档（含项目概述、Git版本历史、提交备注）</t>
-        </is>
-      </c>
-      <c r="H20" s="13" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="I20" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="18" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>248840e</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>248840e9d232eacba69832ed5401065fb3ce1cab</t>
-        </is>
-      </c>
-      <c r="D21" s="18" t="inlineStr">
-        <is>
-          <t>2026-10-13 01:07:27</t>
-        </is>
-      </c>
-      <c r="E21" s="18" t="inlineStr">
-        <is>
-          <t>Jevon Zhu</t>
-        </is>
-      </c>
-      <c r="F21" s="18" t="inlineStr">
-        <is>
-          <t>jevonzhu2008@gmail.com</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>初始化存档：KFM选冶厂月报 Power BI 项目（PBIP）</t>
-        </is>
-      </c>
-      <c r="H21" s="18" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="I21" s="18" t="n">
+      <c r="I22" s="18" t="n">
         <v>61</v>
       </c>
-      <c r="J21" s="18" t="n">
+      <c r="J22" s="18" t="n">
         <v>26750</v>
       </c>
-      <c r="K21" s="18" t="n">
+      <c r="K22" s="18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2342,7 +2376,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A42"/>
+  <dimension ref="A1:A44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="19.95" customHeight="1"/>
   <cols>
     <col width="112" customWidth="1" style="17" min="1" max="1"/>
@@ -2363,14 +2397,33 @@
       </c>
     </row>
     <row r="3" ht="19.95" customHeight="1" s="17">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>提交 03b7f44 ｜ 2026-10-15 10:05:16 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="149.55" customHeight="1" s="17">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>二级指标列改名与入选品位/回收率新口径，同步报表与分析报告
+- 语义模型：「类别2」统一改名为「二级指标」，细分逻辑改按序号驱动；序号/排序/环节序号类型统一 int64
+- 度量值：入选品位精简为 4 个新口径度量值（2 入矿品位 + 2 选冶回收率），删除 8 个基础量
+- 报表：删除一个页面并调整视觉对象与书签
+- 报告：同步更新语义模型分析报告
+Co-Authored-By: Claude Opus 4.8 &lt;noreply@anthropic.com&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="19.95" customHeight="1" s="17">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>提交 6e604e4 ｜ 2026-10-14 18:41:35 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="149.55" customHeight="1" s="17">
-      <c r="A4" s="9" t="inlineStr">
+    <row r="6" ht="118.5" customHeight="1" s="17">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>日报表新增入选品位度量值与指标列，同步月报口径、报表页面与分析报告
 - 日报表：新增「指标名称」「产品分类」两列，类别2/排序改按产品分类细分，输出列 15→17
@@ -2382,15 +2435,15 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="19.95" customHeight="1" s="17">
-      <c r="A5" s="8" t="inlineStr">
+    <row r="7" ht="19.95" customHeight="1" s="17">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>提交 d6b1785 ｜ 2026-10-14 14:05:13 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="118.5" customHeight="1" s="17">
-      <c r="A6" s="9" t="inlineStr">
+    <row r="8" ht="149.55" customHeight="1" s="17">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>重命名报表项目：L3报表-KFM日月报 → L3报表
 - 项目、报告、语义模型整体重命名为 L3报表（目录、.pbip、.platform、definition.pbir 同步更新）
@@ -2401,15 +2454,15 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="19.95" customHeight="1" s="17">
-      <c r="A7" s="8" t="inlineStr">
+    <row r="9" ht="19.95" customHeight="1" s="17">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>提交 8c90e31 ｜ 2026-10-14 12:08:57 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="149.55" customHeight="1" s="17">
-      <c r="A8" s="9" t="inlineStr">
+    <row r="10" ht="133.95" customHeight="1" s="17">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>更新语义模型分析报告：同步 M 优化与列精简
 - 模型总览列数同步：月报 18 列、日报 15 列
@@ -2419,15 +2472,15 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="19.95" customHeight="1" s="17">
-      <c r="A9" s="8" t="inlineStr">
+    <row r="11" ht="19.95" customHeight="1" s="17">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>提交 7148b64 ｜ 2026-10-14 11:35:22 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="133.95" customHeight="1" s="17">
-      <c r="A10" s="9" t="inlineStr">
+    <row r="12" ht="118.5" customHeight="1" s="17">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>优化语义模型 M 代码与输出列
 - 日报新增「日期筛选器」列（按「原矿处理量」最大标准日期标记「最近日期」）
@@ -2439,15 +2492,15 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="19.95" customHeight="1" s="17">
-      <c r="A11" s="8" t="inlineStr">
+    <row r="13" ht="19.95" customHeight="1" s="17">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>提交 f996ae9 ｜ 2026-10-14 11:35:16 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="118.5" customHeight="1" s="17">
-      <c r="A12" s="9" t="inlineStr">
+    <row r="14" ht="118.5" customHeight="1" s="17">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>调整报告页面命名与日报日期筛选
 - 页面更名：KFM选冶厂月报UI Enhance → KFM月报UIE、KFM选冶厂月报 → KFM月报
@@ -2458,15 +2511,15 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="19.95" customHeight="1" s="17">
-      <c r="A13" s="8" t="inlineStr">
+    <row r="15" ht="19.95" customHeight="1" s="17">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>提交 630c17f ｜ 2026-10-14 10:06:29 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="118.5" customHeight="1" s="17">
-      <c r="A14" s="9" t="inlineStr">
+    <row r="16" ht="196.05" customHeight="1" s="17">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>更新语义模型分析报告：同步本轮修复
 - 同步年累计完成L1 新口径与新增参数、中间表变化
@@ -2476,15 +2529,15 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="19.95" customHeight="1" s="17">
-      <c r="A15" s="8" t="inlineStr">
+    <row r="17" ht="19.95" customHeight="1" s="17">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>提交 1794160 ｜ 2026-10-14 10:06:24 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="196.05" customHeight="1" s="17">
-      <c r="A16" s="9" t="inlineStr">
+    <row r="18" ht="118.5" customHeight="1" s="17">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>调整报告视觉对象布局与筛选
 - 按钮/书签视觉对象位置与尺寸微调
@@ -2494,15 +2547,15 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="19.95" customHeight="1" s="17">
-      <c r="A17" s="8" t="inlineStr">
+    <row r="19" ht="19.95" customHeight="1" s="17">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>提交 9cbf408 ｜ 2026-10-14 10:06:18 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="118.5" customHeight="1" s="17">
-      <c r="A18" s="9" t="inlineStr">
+    <row r="20" ht="87.45" customHeight="1" s="17">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>修复语义模型分析报告发现的问题
 - 年累计完成L1 口径修正：累计预测数 → 累计实际数（新增列，经上月编码关联月报），消除重复计算
@@ -2517,15 +2570,15 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="19.95" customHeight="1" s="17">
-      <c r="A19" s="8" t="inlineStr">
+    <row r="21" ht="19.95" customHeight="1" s="17">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>提交 07f180b ｜ 2026-10-14 07:21:58 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="87.45" customHeight="1" s="17">
-      <c r="A20" s="9" t="inlineStr">
+    <row r="22" ht="103.05" customHeight="1" s="17">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>修正日报度量值：清理标题围栏并调整年累计完成字段
 - 标题-日报：移除多余的三反引号围栏标记，修复 TMDL 语法解析
@@ -2535,15 +2588,15 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="19.95" customHeight="1" s="17">
-      <c r="A21" s="8" t="inlineStr">
+    <row r="23" ht="19.95" customHeight="1" s="17">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>提交 2d4f16f ｜ 2026-10-14 07:01:02 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="103.05" customHeight="1" s="17">
-      <c r="A22" s="9" t="inlineStr">
+    <row r="24" ht="118.5" customHeight="1" s="17">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>新增 KFM日月报语义模型分析报告
 HTML 分析报告，涵盖模型总览、M 转换逻辑、DAX 计算逻辑与分级问题清单。
@@ -2551,15 +2604,15 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="19.95" customHeight="1" s="17">
-      <c r="A23" s="8" t="inlineStr">
+    <row r="25" ht="19.95" customHeight="1" s="17">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>提交 5ba71b7 ｜ 2026-10-14 06:57:45 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="118.5" customHeight="1" s="17">
-      <c r="A24" s="9" t="inlineStr">
+    <row r="26" ht="87.45" customHeight="1" s="17">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>修正 DAX/M 代码注释，准确反映实际逻辑
 - functions.tmdl：修正 FormatAmount/FormatRatio 的格式注释（两位小数/差额/百分比），SameMonthPriorYear 顶部注释去掉「年累计实际数」限定
@@ -2568,15 +2621,15 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="19.95" customHeight="1" s="17">
-      <c r="A25" s="8" t="inlineStr">
+    <row r="27" ht="19.95" customHeight="1" s="17">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>提交 cea3882 ｜ 2026-10-14 06:34:36 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="87.45" customHeight="1" s="17">
-      <c r="A26" s="9" t="inlineStr">
+    <row r="28" ht="87.45" customHeight="1" s="17">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>优化语义模型自定义函数命名
 - FormatKFM → FormatAmount（数量格式）
@@ -2586,15 +2639,15 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="19.95" customHeight="1" s="17">
-      <c r="A27" s="8" t="inlineStr">
+    <row r="29" ht="19.95" customHeight="1" s="17">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t>提交 9f32794 ｜ 2026-10-14 06:22:46 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="87.45" customHeight="1" s="17">
-      <c r="A28" s="9" t="inlineStr">
+    <row r="30" ht="103.05" customHeight="1" s="17">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>重命名报表项目：KFM选冶厂月报 → L3报表-KFM日月报
 删除旧项目文件，改用新项目名称。
@@ -2602,15 +2655,15 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="19.95" customHeight="1" s="17">
-      <c r="A29" s="8" t="inlineStr">
+    <row r="31" ht="19.95" customHeight="1" s="17">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>提交 07301c6 ｜ 2026-10-13 19:57:45 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="103.05" customHeight="1" s="17">
-      <c r="A30" s="9" t="inlineStr">
+    <row r="32" ht="133.95" customHeight="1" s="17">
+      <c r="A32" s="9" t="inlineStr">
         <is>
           <t>修复 KFM选冶厂月报 TMDL 缩进错误
 将 source 的 M 代码改为三反引号形式，修复 let 顶格导致的 TMDL 缩进解析错误。
@@ -2618,15 +2671,15 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="19.95" customHeight="1" s="17">
-      <c r="A31" s="8" t="inlineStr">
+    <row r="33" ht="19.95" customHeight="1" s="17">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>提交 1485d55 ｜ 2026-10-13 19:45:55 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="133.95" customHeight="1" s="17">
-      <c r="A32" s="9" t="inlineStr">
+    <row r="34" ht="133.95" customHeight="1" s="17">
+      <c r="A34" s="9" t="inlineStr">
         <is>
           <t>优化全部 M 查询：步骤名语义化与步骤合并
 - KFM选冶厂月报：Cube.Transform 直接输出最终列名，删除「重命名列」「新增指标项列」步骤；去掉未使用的产品、矿坑、指标编码维度；合并类别2分组逻辑与最近月份计算；步骤名统一中文
@@ -2635,15 +2688,15 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="19.95" customHeight="1" s="17">
-      <c r="A33" s="8" t="inlineStr">
+    <row r="35" ht="19.95" customHeight="1" s="17">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>提交 6b4084c ｜ 2026-10-13 19:31:50 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="133.95" customHeight="1" s="17">
-      <c r="A34" s="9" t="inlineStr">
+    <row r="36" ht="273.45" customHeight="1" s="17">
+      <c r="A36" s="9" t="inlineStr">
         <is>
           <t>优化L1-KFM日报 M 查询：命名注释与步骤精简
 - Cube.Transform 直接输出最终列名，删除冗余的「重命名的列」步骤
@@ -2654,15 +2707,15 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="19.95" customHeight="1" s="17">
-      <c r="A35" s="8" t="inlineStr">
+    <row r="37" ht="19.95" customHeight="1" s="17">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>提交 2a59e2f ｜ 2026-10-13 19:15:18 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="273.45" customHeight="1" s="17">
-      <c r="A36" s="9" t="inlineStr">
+    <row r="38" ht="56.55" customHeight="1" s="17">
+      <c r="A38" s="9" t="inlineStr">
         <is>
           <t>优化L1-KFM日报 M 查询：内联两个中间表
 - 将 全年预算表、月累计预测表 两个中间表 expression 内联进 L1-KFM日报 的 M 查询，消除跨查询依赖
@@ -2673,15 +2726,15 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="19.95" customHeight="1" s="17">
-      <c r="A37" s="8" t="inlineStr">
+    <row r="39" ht="19.95" customHeight="1" s="17">
+      <c r="A39" s="8" t="inlineStr">
         <is>
           <t>提交 48112a2 ｜ 2026-10-13 18:55:27 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="56.55" customHeight="1" s="17">
-      <c r="A38" s="9" t="inlineStr">
+    <row r="40" ht="409.6" customHeight="1" s="17">
+      <c r="A40" s="9" t="inlineStr">
         <is>
           <t>升级语义模型兼容级别1702，新增日报模型与DAX函数(UDF)
 语义模型
@@ -2700,30 +2753,30 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="19.95" customHeight="1" s="17">
-      <c r="A39" s="8" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="8" t="inlineStr">
         <is>
           <t>提交 69bb2ba ｜ 2026-10-13 01:42:09 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="409.6" customHeight="1" s="17">
-      <c r="A40" s="9" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="9" t="inlineStr">
         <is>
           <t>新增项目版本信息 Excel 文档（含项目概述、Git版本历史、提交备注）
 Co-Authored-By: Claude Fable 5.1 &lt;noreply@anthropic.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="8" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="8" t="inlineStr">
         <is>
           <t>提交 248840e ｜ 2026-10-13 01:07:27 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="9" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="9" t="inlineStr">
         <is>
           <t>初始化存档：KFM选冶厂月报 Power BI 项目（PBIP）
 项目概述
@@ -2963,13 +3016,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BD6072F-03C3-416E-90BD-16FD571037B3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{02B32B95-2E6E-4435-B751-86B8FD913EDD}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9069709A-B999-43B3-98E6-1D7CEA828869}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73E0F6B6-9504-42BE-A47E-66B81F16B99D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D8F66E42-1063-4B94-A7CE-FC9026EE5EEC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54739EE9-52E6-4210-99DF-0EEB50353E6F}"/>
 </file>
--- a/L3报表项目版本信息.xlsx
+++ b/L3报表项目版本信息.xlsx
@@ -834,8 +834,8 @@
           <t>主题：Fluent2 基础主题 + 自定义主题，注册 2 张背景图片</t>
         </is>
       </c>
-      <c r="B10" s="14" t="n"/>
-      <c r="C10" s="14" t="n"/>
+      <c r="B10" s="15" t="n"/>
+      <c r="C10" s="15" t="n"/>
       <c r="D10" s="14" t="n"/>
       <c r="E10" s="14" t="n"/>
       <c r="F10" s="15" t="n"/>
@@ -867,16 +867,11 @@
           <t>累计实际数</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>累计预测数</t>
-        </is>
-      </c>
-      <c r="E14" s="1" t="inlineStr">
-        <is>
-          <t>累计预算数</t>
-        </is>
-      </c>
+      <c r="B14" s="14" t="n"/>
+      <c r="C14" s="14" t="n"/>
+      <c r="D14" s="14" t="n"/>
+      <c r="E14" s="14" t="n"/>
+      <c r="F14" s="15" t="n"/>
     </row>
     <row r="15" ht="19.95" customHeight="1" s="17">
       <c r="A15" s="1" t="inlineStr">
@@ -983,16 +978,11 @@
           <t>单位</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>当日实际数</t>
-        </is>
-      </c>
-      <c r="E22" s="1" t="inlineStr">
-        <is>
-          <t>当月累计实际数</t>
-        </is>
-      </c>
+      <c r="B22" s="14" t="n"/>
+      <c r="C22" s="14" t="n"/>
+      <c r="D22" s="14" t="n"/>
+      <c r="E22" s="14" t="n"/>
+      <c r="F22" s="15" t="n"/>
     </row>
     <row r="23" ht="19.95" customHeight="1" s="17">
       <c r="A23" s="1" t="inlineStr">
@@ -1108,31 +1098,11 @@
           <t>序号</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>指标项</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>类别</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>环节</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>环节序号</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>报表</t>
-        </is>
-      </c>
+      <c r="B33" s="14" t="n"/>
+      <c r="C33" s="14" t="n"/>
+      <c r="D33" s="14" t="n"/>
+      <c r="E33" s="14" t="n"/>
+      <c r="F33" s="15" t="n"/>
     </row>
     <row r="34" ht="34.95" customHeight="1" s="17">
       <c r="A34" s="16" t="inlineStr">
@@ -1264,7 +1234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="5" customWidth="1" style="17" min="1" max="1"/>
@@ -1342,96 +1312,96 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>3383b89</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>3383b89a26c058fe8288116492857b5876884703</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-10-15 10:27:59</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>度量值显示文件夹加数字前缀排序并改名新口径</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J2" t="n">
+        <v>56</v>
+      </c>
+      <c r="K2" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1" s="17">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>03b7f44</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>03b7f44d157dc79e23a7b3cd8c6f93bbdc3b36a4</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>2026-10-15 10:05:16</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Jevon Zhu</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>jevonzhu2008@gmail.com</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>二级指标列改名与入选品位/回收率新口径，同步报表与分析报告</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="I2" t="n">
+      <c r="I3" t="n">
         <v>34</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J3" t="n">
         <v>348</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K3" t="n">
         <v>10809</v>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1" s="17">
-      <c r="A3" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="13" t="inlineStr">
-        <is>
-          <t>6e604e4</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>6e604e4d0315cd3426b5f37097aed19041b27654</t>
-        </is>
-      </c>
-      <c r="D3" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-14 18:41:35</t>
-        </is>
-      </c>
-      <c r="E3" s="13" t="inlineStr">
-        <is>
-          <t>Jevon Zhu</t>
-        </is>
-      </c>
-      <c r="F3" s="13" t="inlineStr">
-        <is>
-          <t>jevonzhu2008@gmail.com</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>日报表新增入选品位度量值与指标列，同步月报口径、报表页面与分析报告</t>
-        </is>
-      </c>
-      <c r="H3" s="13" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="I3" s="13" t="n">
-        <v>18</v>
-      </c>
-      <c r="J3" s="13" t="n">
-        <v>1565</v>
-      </c>
-      <c r="K3" s="13" t="n">
-        <v>175</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" s="17">
@@ -1440,17 +1410,17 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>d6b1785</t>
+          <t>6e604e4</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>d6b1785b86f19f2db61866bfc840abcac3e1f2cf</t>
+          <t>6e604e4d0315cd3426b5f37097aed19041b27654</t>
         </is>
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>2026-10-14 14:05:13</t>
+          <t>2026-10-14 18:41:35</t>
         </is>
       </c>
       <c r="E4" s="13" t="inlineStr">
@@ -1465,7 +1435,7 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>重命名报表项目：L3报表-KFM日月报 → L3报表</t>
+          <t>日报表新增入选品位度量值与指标列，同步月报口径、报表页面与分析报告</t>
         </is>
       </c>
       <c r="H4" s="13" t="inlineStr">
@@ -1474,13 +1444,13 @@
         </is>
       </c>
       <c r="I4" s="13" t="n">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="J4" s="13" t="n">
-        <v>23</v>
+        <v>1565</v>
       </c>
       <c r="K4" s="13" t="n">
-        <v>17</v>
+        <v>175</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" s="17">
@@ -1489,879 +1459,928 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
+          <t>d6b1785</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>d6b1785b86f19f2db61866bfc840abcac3e1f2cf</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-14 14:05:13</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F5" s="13" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>重命名报表项目：L3报表-KFM日月报 → L3报表</t>
+        </is>
+      </c>
+      <c r="H5" s="13" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I5" s="13" t="n">
+        <v>68</v>
+      </c>
+      <c r="J5" s="13" t="n">
+        <v>23</v>
+      </c>
+      <c r="K5" s="13" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1" s="17">
+      <c r="A6" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
           <t>8c90e31</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>8c90e3154248a749ec3ef3bc61d68576b709d2f7</t>
         </is>
       </c>
-      <c r="D5" s="13" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>2026-10-14 12:08:57</t>
         </is>
       </c>
-      <c r="E5" s="13" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>Jevon Zhu</t>
         </is>
       </c>
-      <c r="F5" s="13" t="inlineStr">
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t>jevonzhu2008@gmail.com</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>更新语义模型分析报告：同步 M 优化与列精简</t>
         </is>
       </c>
-      <c r="H5" s="13" t="inlineStr">
+      <c r="H6" s="13" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="I5" s="13" t="n">
+      <c r="I6" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="J5" s="13" t="n">
+      <c r="J6" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="K5" s="13" t="n">
+      <c r="K6" s="13" t="n">
         <v>16</v>
       </c>
     </row>
-    <row r="6" ht="30" customHeight="1" s="17">
-      <c r="A6" s="18" t="n">
+    <row r="7" ht="30" customHeight="1" s="17">
+      <c r="A7" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="18" t="inlineStr">
+        <is>
+          <t>7148b64</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>7148b64ddd4ee32a7c06e2f912d939dc2ba4e1b5</t>
+        </is>
+      </c>
+      <c r="D7" s="18" t="inlineStr">
+        <is>
+          <t>2026-10-14 11:35:22</t>
+        </is>
+      </c>
+      <c r="E7" s="18" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F7" s="18" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>优化语义模型 M 代码与输出列</t>
+        </is>
+      </c>
+      <c r="H7" s="18" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I7" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="18" t="inlineStr">
-        <is>
-          <t>7148b64</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>7148b64ddd4ee32a7c06e2f912d939dc2ba4e1b5</t>
-        </is>
-      </c>
-      <c r="D6" s="18" t="inlineStr">
-        <is>
-          <t>2026-10-14 11:35:22</t>
-        </is>
-      </c>
-      <c r="E6" s="18" t="inlineStr">
+      <c r="J7" s="18" t="n">
+        <v>38</v>
+      </c>
+      <c r="K7" s="18" t="n">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1" s="17">
+      <c r="A8" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>f996ae9</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>f996ae982e67b13a495117c8a9b34531f4eded82</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-14 11:35:16</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
         <is>
           <t>Jevon Zhu</t>
         </is>
       </c>
-      <c r="F6" s="18" t="inlineStr">
+      <c r="F8" s="13" t="inlineStr">
         <is>
           <t>jevonzhu2008@gmail.com</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>优化语义模型 M 代码与输出列</t>
-        </is>
-      </c>
-      <c r="H6" s="18" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>调整报告页面命名与日报日期筛选</t>
+        </is>
+      </c>
+      <c r="H8" s="13" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="I6" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="J6" s="18" t="n">
-        <v>38</v>
-      </c>
-      <c r="K6" s="18" t="n">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1" s="17">
-      <c r="A7" s="13" t="n">
+      <c r="I8" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>f996ae9</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>f996ae982e67b13a495117c8a9b34531f4eded82</t>
-        </is>
-      </c>
-      <c r="D7" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-14 11:35:16</t>
-        </is>
-      </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="J8" s="13" t="n">
+        <v>133</v>
+      </c>
+      <c r="K8" s="13" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1" s="17">
+      <c r="A9" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t>630c17f</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>630c17fceaf47b46c21633e044fda78155ac0443</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="inlineStr">
+        <is>
+          <t>2026-10-14 10:06:29</t>
+        </is>
+      </c>
+      <c r="E9" s="18" t="inlineStr">
         <is>
           <t>Jevon Zhu</t>
         </is>
       </c>
-      <c r="F7" s="13" t="inlineStr">
+      <c r="F9" s="18" t="inlineStr">
         <is>
           <t>jevonzhu2008@gmail.com</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>调整报告页面命名与日报日期筛选</t>
-        </is>
-      </c>
-      <c r="H7" s="13" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>更新语义模型分析报告：同步本轮修复</t>
+        </is>
+      </c>
+      <c r="H9" s="18" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="I7" s="13" t="n">
+      <c r="I9" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="18" t="n">
+        <v>35</v>
+      </c>
+      <c r="K9" s="18" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1" s="17">
+      <c r="A10" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>1794160</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>179416093e3aff5472f3a2f4719d2270cff850d1</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-14 10:06:24</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>调整报告视觉对象布局与筛选</t>
+        </is>
+      </c>
+      <c r="H10" s="13" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I10" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="J10" s="13" t="n">
+        <v>37</v>
+      </c>
+      <c r="K10" s="13" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1" s="17">
+      <c r="A11" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t>9cbf408</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>9cbf408d9186e1be6583b91b3e445288720dab30</t>
+        </is>
+      </c>
+      <c r="D11" s="18" t="inlineStr">
+        <is>
+          <t>2026-10-14 10:06:18</t>
+        </is>
+      </c>
+      <c r="E11" s="18" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F11" s="18" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>修复语义模型分析报告发现的问题</t>
+        </is>
+      </c>
+      <c r="H11" s="18" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I11" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="J11" s="18" t="n">
+        <v>86</v>
+      </c>
+      <c r="K11" s="18" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1" s="17">
+      <c r="A12" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>07f180b</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>07f180b9740c0c72f4ff4cb637acce0c8b718efc</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-14 07:21:58</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F12" s="13" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>修正日报度量值：清理标题围栏并调整年累计完成字段</t>
+        </is>
+      </c>
+      <c r="H12" s="13" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I12" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="K12" s="13" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1" s="17">
+      <c r="A13" s="18" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="18" t="inlineStr">
+        <is>
+          <t>2d4f16f</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>2d4f16fda737382909dd93ca2b175b6618fcbb57</t>
+        </is>
+      </c>
+      <c r="D13" s="18" t="inlineStr">
+        <is>
+          <t>2026-10-14 07:01:02</t>
+        </is>
+      </c>
+      <c r="E13" s="18" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F13" s="18" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>新增 KFM日月报语义模型分析报告</t>
+        </is>
+      </c>
+      <c r="H13" s="18" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I13" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" s="18" t="n">
+        <v>320</v>
+      </c>
+      <c r="K13" s="18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1" s="17">
+      <c r="A14" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>5ba71b7</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>5ba71b7bdd8c9fa3140791e2c325425796229e13</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-14 06:57:45</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F14" s="13" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>修正 DAX/M 代码注释，准确反映实际逻辑</t>
+        </is>
+      </c>
+      <c r="H14" s="13" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I14" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="J14" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="K14" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="J7" s="13" t="n">
-        <v>133</v>
-      </c>
-      <c r="K7" s="13" t="n">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1" s="17">
-      <c r="A8" s="18" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>630c17f</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>630c17fceaf47b46c21633e044fda78155ac0443</t>
-        </is>
-      </c>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>2026-10-14 10:06:29</t>
-        </is>
-      </c>
-      <c r="E8" s="18" t="inlineStr">
+    </row>
+    <row r="15" ht="30" customHeight="1" s="17">
+      <c r="A15" s="18" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="18" t="inlineStr">
+        <is>
+          <t>cea3882</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>cea3882903b1e0ebd284ee0a2acadb18380ddd7f</t>
+        </is>
+      </c>
+      <c r="D15" s="18" t="inlineStr">
+        <is>
+          <t>2026-10-14 06:34:36</t>
+        </is>
+      </c>
+      <c r="E15" s="18" t="inlineStr">
         <is>
           <t>Jevon Zhu</t>
         </is>
       </c>
-      <c r="F8" s="18" t="inlineStr">
+      <c r="F15" s="18" t="inlineStr">
         <is>
           <t>jevonzhu2008@gmail.com</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>更新语义模型分析报告：同步本轮修复</t>
-        </is>
-      </c>
-      <c r="H8" s="18" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>优化语义模型自定义函数命名</t>
+        </is>
+      </c>
+      <c r="H15" s="18" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="I8" s="18" t="n">
+      <c r="I15" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="J15" s="18" t="n">
+        <v>17</v>
+      </c>
+      <c r="K15" s="18" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1" s="17">
+      <c r="A16" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>9f32794</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>9f32794cc45bd00e695f720d0e38ca7eda0ee97d</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-14 06:22:46</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F16" s="13" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>重命名报表项目：KFM选冶厂月报 → L3报表-KFM日月报</t>
+        </is>
+      </c>
+      <c r="H16" s="13" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I16" s="13" t="n">
+        <v>70</v>
+      </c>
+      <c r="J16" s="13" t="n">
+        <v>695</v>
+      </c>
+      <c r="K16" s="13" t="n">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1" s="17">
+      <c r="A17" s="18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="18" t="inlineStr">
+        <is>
+          <t>07301c6</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>07301c63639499dc1642f9abe29a9baee1e0c3cf</t>
+        </is>
+      </c>
+      <c r="D17" s="18" t="inlineStr">
+        <is>
+          <t>2026-10-13 19:57:45</t>
+        </is>
+      </c>
+      <c r="E17" s="18" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F17" s="18" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>修复 KFM选冶厂月报 TMDL 缩进错误</t>
+        </is>
+      </c>
+      <c r="H17" s="18" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I17" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="J8" s="18" t="n">
+      <c r="J17" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1" s="17">
+      <c r="A18" s="13" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>1485d55</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>1485d55c4d5b2c241eb05e9040a3897476085331</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-13 19:45:55</t>
+        </is>
+      </c>
+      <c r="E18" s="13" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F18" s="13" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>优化全部 M 查询：步骤名语义化与步骤合并</t>
+        </is>
+      </c>
+      <c r="H18" s="13" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I18" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="J18" s="13" t="n">
+        <v>134</v>
+      </c>
+      <c r="K18" s="13" t="n">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1" s="17">
+      <c r="A19" s="18" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="18" t="inlineStr">
+        <is>
+          <t>6b4084c</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>6b4084c9a3fb078c53fcbdd2549a2adc1fc7d100</t>
+        </is>
+      </c>
+      <c r="D19" s="18" t="inlineStr">
+        <is>
+          <t>2026-10-13 19:31:50</t>
+        </is>
+      </c>
+      <c r="E19" s="18" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F19" s="18" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>优化L1-KFM日报 M 查询：命名注释与步骤精简</t>
+        </is>
+      </c>
+      <c r="H19" s="18" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I19" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" s="18" t="n">
+        <v>130</v>
+      </c>
+      <c r="K19" s="18" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1" s="17">
+      <c r="A20" s="13" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>2a59e2f</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>2a59e2f68de3a82d02c6493c75d4a170ce013fae</t>
+        </is>
+      </c>
+      <c r="D20" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-13 19:15:18</t>
+        </is>
+      </c>
+      <c r="E20" s="13" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F20" s="13" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>优化L1-KFM日报 M 查询：内联两个中间表</t>
+        </is>
+      </c>
+      <c r="H20" s="13" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I20" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="J20" s="13" t="n">
+        <v>21</v>
+      </c>
+      <c r="K20" s="13" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="18" t="inlineStr">
+        <is>
+          <t>48112a2</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>48112a2bfe1b2809ef94fe779a2e7a6c65d60bb2</t>
+        </is>
+      </c>
+      <c r="D21" s="18" t="inlineStr">
+        <is>
+          <t>2026-10-13 18:55:27</t>
+        </is>
+      </c>
+      <c r="E21" s="18" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F21" s="18" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>升级语义模型兼容级别1702，新增日报模型与DAX函数(UDF)</t>
+        </is>
+      </c>
+      <c r="H21" s="18" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I21" s="18" t="n">
         <v>35</v>
       </c>
-      <c r="K8" s="18" t="n">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1" s="17">
-      <c r="A9" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>1794160</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>179416093e3aff5472f3a2f4719d2270cff850d1</t>
-        </is>
-      </c>
-      <c r="D9" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-14 10:06:24</t>
-        </is>
-      </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="J21" s="18" t="n">
+        <v>5662</v>
+      </c>
+      <c r="K21" s="18" t="n">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>69bb2ba</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>69bb2ba9dc7aa839a00235f2ef0ed1b691d7384e</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-13 01:42:09</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="inlineStr">
         <is>
           <t>Jevon Zhu</t>
         </is>
       </c>
-      <c r="F9" s="13" t="inlineStr">
+      <c r="F22" s="13" t="inlineStr">
         <is>
           <t>jevonzhu2008@gmail.com</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>调整报告视觉对象布局与筛选</t>
-        </is>
-      </c>
-      <c r="H9" s="13" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>新增项目版本信息 Excel 文档（含项目概述、Git版本历史、提交备注）</t>
+        </is>
+      </c>
+      <c r="H22" s="13" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="I9" s="13" t="n">
-        <v>7</v>
-      </c>
-      <c r="J9" s="13" t="n">
-        <v>37</v>
-      </c>
-      <c r="K9" s="13" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1" s="17">
-      <c r="A10" s="18" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>9cbf408</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>9cbf408d9186e1be6583b91b3e445288720dab30</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="inlineStr">
-        <is>
-          <t>2026-10-14 10:06:18</t>
-        </is>
-      </c>
-      <c r="E10" s="18" t="inlineStr">
+      <c r="I22" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="18" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="18" t="inlineStr">
+        <is>
+          <t>248840e</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>248840e9d232eacba69832ed5401065fb3ce1cab</t>
+        </is>
+      </c>
+      <c r="D23" s="18" t="inlineStr">
+        <is>
+          <t>2026-10-13 01:07:27</t>
+        </is>
+      </c>
+      <c r="E23" s="18" t="inlineStr">
         <is>
           <t>Jevon Zhu</t>
         </is>
       </c>
-      <c r="F10" s="18" t="inlineStr">
+      <c r="F23" s="18" t="inlineStr">
         <is>
           <t>jevonzhu2008@gmail.com</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>修复语义模型分析报告发现的问题</t>
-        </is>
-      </c>
-      <c r="H10" s="18" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>初始化存档：KFM选冶厂月报 Power BI 项目（PBIP）</t>
+        </is>
+      </c>
+      <c r="H23" s="18" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="I10" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="J10" s="18" t="n">
-        <v>86</v>
-      </c>
-      <c r="K10" s="18" t="n">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1" s="17">
-      <c r="A11" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>07f180b</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>07f180b9740c0c72f4ff4cb637acce0c8b718efc</t>
-        </is>
-      </c>
-      <c r="D11" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-14 07:21:58</t>
-        </is>
-      </c>
-      <c r="E11" s="13" t="inlineStr">
-        <is>
-          <t>Jevon Zhu</t>
-        </is>
-      </c>
-      <c r="F11" s="13" t="inlineStr">
-        <is>
-          <t>jevonzhu2008@gmail.com</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>修正日报度量值：清理标题围栏并调整年累计完成字段</t>
-        </is>
-      </c>
-      <c r="H11" s="13" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="I11" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="K11" s="13" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1" s="17">
-      <c r="A12" s="18" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>2d4f16f</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>2d4f16fda737382909dd93ca2b175b6618fcbb57</t>
-        </is>
-      </c>
-      <c r="D12" s="18" t="inlineStr">
-        <is>
-          <t>2026-10-14 07:01:02</t>
-        </is>
-      </c>
-      <c r="E12" s="18" t="inlineStr">
-        <is>
-          <t>Jevon Zhu</t>
-        </is>
-      </c>
-      <c r="F12" s="18" t="inlineStr">
-        <is>
-          <t>jevonzhu2008@gmail.com</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>新增 KFM日月报语义模型分析报告</t>
-        </is>
-      </c>
-      <c r="H12" s="18" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="I12" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" s="18" t="n">
-        <v>320</v>
-      </c>
-      <c r="K12" s="18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1" s="17">
-      <c r="A13" s="13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="13" t="inlineStr">
-        <is>
-          <t>5ba71b7</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>5ba71b7bdd8c9fa3140791e2c325425796229e13</t>
-        </is>
-      </c>
-      <c r="D13" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-14 06:57:45</t>
-        </is>
-      </c>
-      <c r="E13" s="13" t="inlineStr">
-        <is>
-          <t>Jevon Zhu</t>
-        </is>
-      </c>
-      <c r="F13" s="13" t="inlineStr">
-        <is>
-          <t>jevonzhu2008@gmail.com</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>修正 DAX/M 代码注释，准确反映实际逻辑</t>
-        </is>
-      </c>
-      <c r="H13" s="13" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="I13" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="J13" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="K13" s="13" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1" s="17">
-      <c r="A14" s="18" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>cea3882</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>cea3882903b1e0ebd284ee0a2acadb18380ddd7f</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>2026-10-14 06:34:36</t>
-        </is>
-      </c>
-      <c r="E14" s="18" t="inlineStr">
-        <is>
-          <t>Jevon Zhu</t>
-        </is>
-      </c>
-      <c r="F14" s="18" t="inlineStr">
-        <is>
-          <t>jevonzhu2008@gmail.com</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>优化语义模型自定义函数命名</t>
-        </is>
-      </c>
-      <c r="H14" s="18" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="I14" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="J14" s="18" t="n">
-        <v>17</v>
-      </c>
-      <c r="K14" s="18" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1" s="17">
-      <c r="A15" s="13" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="13" t="inlineStr">
-        <is>
-          <t>9f32794</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>9f32794cc45bd00e695f720d0e38ca7eda0ee97d</t>
-        </is>
-      </c>
-      <c r="D15" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-14 06:22:46</t>
-        </is>
-      </c>
-      <c r="E15" s="13" t="inlineStr">
-        <is>
-          <t>Jevon Zhu</t>
-        </is>
-      </c>
-      <c r="F15" s="13" t="inlineStr">
-        <is>
-          <t>jevonzhu2008@gmail.com</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>重命名报表项目：KFM选冶厂月报 → L3报表-KFM日月报</t>
-        </is>
-      </c>
-      <c r="H15" s="13" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="I15" s="13" t="n">
-        <v>70</v>
-      </c>
-      <c r="J15" s="13" t="n">
-        <v>695</v>
-      </c>
-      <c r="K15" s="13" t="n">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1" s="17">
-      <c r="A16" s="18" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>07301c6</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>07301c63639499dc1642f9abe29a9baee1e0c3cf</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="inlineStr">
-        <is>
-          <t>2026-10-13 19:57:45</t>
-        </is>
-      </c>
-      <c r="E16" s="18" t="inlineStr">
-        <is>
-          <t>Jevon Zhu</t>
-        </is>
-      </c>
-      <c r="F16" s="18" t="inlineStr">
-        <is>
-          <t>jevonzhu2008@gmail.com</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>修复 KFM选冶厂月报 TMDL 缩进错误</t>
-        </is>
-      </c>
-      <c r="H16" s="18" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="I16" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="J16" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="K16" s="18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1" s="17">
-      <c r="A17" s="13" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="13" t="inlineStr">
-        <is>
-          <t>1485d55</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>1485d55c4d5b2c241eb05e9040a3897476085331</t>
-        </is>
-      </c>
-      <c r="D17" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-13 19:45:55</t>
-        </is>
-      </c>
-      <c r="E17" s="13" t="inlineStr">
-        <is>
-          <t>Jevon Zhu</t>
-        </is>
-      </c>
-      <c r="F17" s="13" t="inlineStr">
-        <is>
-          <t>jevonzhu2008@gmail.com</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>优化全部 M 查询：步骤名语义化与步骤合并</t>
-        </is>
-      </c>
-      <c r="H17" s="13" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="I17" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="J17" s="13" t="n">
-        <v>134</v>
-      </c>
-      <c r="K17" s="13" t="n">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1" s="17">
-      <c r="A18" s="18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>6b4084c</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>6b4084c9a3fb078c53fcbdd2549a2adc1fc7d100</t>
-        </is>
-      </c>
-      <c r="D18" s="18" t="inlineStr">
-        <is>
-          <t>2026-10-13 19:31:50</t>
-        </is>
-      </c>
-      <c r="E18" s="18" t="inlineStr">
-        <is>
-          <t>Jevon Zhu</t>
-        </is>
-      </c>
-      <c r="F18" s="18" t="inlineStr">
-        <is>
-          <t>jevonzhu2008@gmail.com</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>优化L1-KFM日报 M 查询：命名注释与步骤精简</t>
-        </is>
-      </c>
-      <c r="H18" s="18" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="I18" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" s="18" t="n">
-        <v>130</v>
-      </c>
-      <c r="K18" s="18" t="n">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1" s="17">
-      <c r="A19" s="13" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="13" t="inlineStr">
-        <is>
-          <t>2a59e2f</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>2a59e2f68de3a82d02c6493c75d4a170ce013fae</t>
-        </is>
-      </c>
-      <c r="D19" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-13 19:15:18</t>
-        </is>
-      </c>
-      <c r="E19" s="13" t="inlineStr">
-        <is>
-          <t>Jevon Zhu</t>
-        </is>
-      </c>
-      <c r="F19" s="13" t="inlineStr">
-        <is>
-          <t>jevonzhu2008@gmail.com</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>优化L1-KFM日报 M 查询：内联两个中间表</t>
-        </is>
-      </c>
-      <c r="H19" s="13" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="I19" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="J19" s="13" t="n">
-        <v>21</v>
-      </c>
-      <c r="K19" s="13" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="20" ht="30" customHeight="1" s="17">
-      <c r="A20" s="18" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>48112a2</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>48112a2bfe1b2809ef94fe779a2e7a6c65d60bb2</t>
-        </is>
-      </c>
-      <c r="D20" s="18" t="inlineStr">
-        <is>
-          <t>2026-10-13 18:55:27</t>
-        </is>
-      </c>
-      <c r="E20" s="18" t="inlineStr">
-        <is>
-          <t>Jevon Zhu</t>
-        </is>
-      </c>
-      <c r="F20" s="18" t="inlineStr">
-        <is>
-          <t>jevonzhu2008@gmail.com</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>升级语义模型兼容级别1702，新增日报模型与DAX函数(UDF)</t>
-        </is>
-      </c>
-      <c r="H20" s="18" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="I20" s="18" t="n">
-        <v>35</v>
-      </c>
-      <c r="J20" s="18" t="n">
-        <v>5662</v>
-      </c>
-      <c r="K20" s="18" t="n">
-        <v>771</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="13" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="13" t="inlineStr">
-        <is>
-          <t>69bb2ba</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>69bb2ba9dc7aa839a00235f2ef0ed1b691d7384e</t>
-        </is>
-      </c>
-      <c r="D21" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-13 01:42:09</t>
-        </is>
-      </c>
-      <c r="E21" s="13" t="inlineStr">
-        <is>
-          <t>Jevon Zhu</t>
-        </is>
-      </c>
-      <c r="F21" s="13" t="inlineStr">
-        <is>
-          <t>jevonzhu2008@gmail.com</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>新增项目版本信息 Excel 文档（含项目概述、Git版本历史、提交备注）</t>
-        </is>
-      </c>
-      <c r="H21" s="13" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="I21" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="18" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>248840e</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>248840e9d232eacba69832ed5401065fb3ce1cab</t>
-        </is>
-      </c>
-      <c r="D22" s="18" t="inlineStr">
-        <is>
-          <t>2026-10-13 01:07:27</t>
-        </is>
-      </c>
-      <c r="E22" s="18" t="inlineStr">
-        <is>
-          <t>Jevon Zhu</t>
-        </is>
-      </c>
-      <c r="F22" s="18" t="inlineStr">
-        <is>
-          <t>jevonzhu2008@gmail.com</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="inlineStr">
-        <is>
-          <t>初始化存档：KFM选冶厂月报 Power BI 项目（PBIP）</t>
-        </is>
-      </c>
-      <c r="H22" s="18" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="I22" s="18" t="n">
+      <c r="I23" s="18" t="n">
         <v>61</v>
       </c>
-      <c r="J22" s="18" t="n">
+      <c r="J23" s="18" t="n">
         <v>26750</v>
       </c>
-      <c r="K22" s="18" t="n">
+      <c r="K23" s="18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2376,7 +2395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A44"/>
+  <dimension ref="A1:A46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="19.95" customHeight="1"/>
   <cols>
     <col width="112" customWidth="1" style="17" min="1" max="1"/>
@@ -2399,12 +2418,30 @@
     <row r="3" ht="19.95" customHeight="1" s="17">
       <c r="A3" t="inlineStr">
         <is>
-          <t>提交 03b7f44 ｜ 2026-10-15 10:05:16 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
+          <t>提交 3383b89 ｜ 2026-10-15 10:27:59 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
     <row r="4" ht="149.55" customHeight="1" s="17">
       <c r="A4" t="inlineStr">
+        <is>
+          <t>度量值显示文件夹加数字前缀排序并改名新口径
+- 度量值 displayFolder 加数字前缀：00辅助 / 02月报 / 03日报，「入选品位」改名「01新口径」
+- L1-KFM日报 M 查询引用规范化（去掉引号与 # 号）
+- 报表活动页切回「日报」，同步布局与页面配置
+Co-Authored-By: Claude Opus 4.8 &lt;noreply@anthropic.com&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="19.95" customHeight="1" s="17">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>提交 03b7f44 ｜ 2026-10-15 10:05:16 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="118.5" customHeight="1" s="17">
+      <c r="A6" t="inlineStr">
         <is>
           <t>二级指标列改名与入选品位/回收率新口径，同步报表与分析报告
 - 语义模型：「类别2」统一改名为「二级指标」，细分逻辑改按序号驱动；序号/排序/环节序号类型统一 int64
@@ -2415,15 +2452,15 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="19.95" customHeight="1" s="17">
-      <c r="A5" s="8" t="inlineStr">
+    <row r="7" ht="19.95" customHeight="1" s="17">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>提交 6e604e4 ｜ 2026-10-14 18:41:35 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="118.5" customHeight="1" s="17">
-      <c r="A6" s="9" t="inlineStr">
+    <row r="8" ht="149.55" customHeight="1" s="17">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>日报表新增入选品位度量值与指标列，同步月报口径、报表页面与分析报告
 - 日报表：新增「指标名称」「产品分类」两列，类别2/排序改按产品分类细分，输出列 15→17
@@ -2435,15 +2472,15 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="19.95" customHeight="1" s="17">
-      <c r="A7" s="8" t="inlineStr">
+    <row r="9" ht="19.95" customHeight="1" s="17">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>提交 d6b1785 ｜ 2026-10-14 14:05:13 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="149.55" customHeight="1" s="17">
-      <c r="A8" s="9" t="inlineStr">
+    <row r="10" ht="133.95" customHeight="1" s="17">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>重命名报表项目：L3报表-KFM日月报 → L3报表
 - 项目、报告、语义模型整体重命名为 L3报表（目录、.pbip、.platform、definition.pbir 同步更新）
@@ -2454,15 +2491,15 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="19.95" customHeight="1" s="17">
-      <c r="A9" s="8" t="inlineStr">
+    <row r="11" ht="19.95" customHeight="1" s="17">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>提交 8c90e31 ｜ 2026-10-14 12:08:57 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="133.95" customHeight="1" s="17">
-      <c r="A10" s="9" t="inlineStr">
+    <row r="12" ht="118.5" customHeight="1" s="17">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>更新语义模型分析报告：同步 M 优化与列精简
 - 模型总览列数同步：月报 18 列、日报 15 列
@@ -2472,15 +2509,15 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="19.95" customHeight="1" s="17">
-      <c r="A11" s="8" t="inlineStr">
+    <row r="13" ht="19.95" customHeight="1" s="17">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>提交 7148b64 ｜ 2026-10-14 11:35:22 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="118.5" customHeight="1" s="17">
-      <c r="A12" s="9" t="inlineStr">
+    <row r="14" ht="118.5" customHeight="1" s="17">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>优化语义模型 M 代码与输出列
 - 日报新增「日期筛选器」列（按「原矿处理量」最大标准日期标记「最近日期」）
@@ -2492,15 +2529,15 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="19.95" customHeight="1" s="17">
-      <c r="A13" s="8" t="inlineStr">
+    <row r="15" ht="19.95" customHeight="1" s="17">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>提交 f996ae9 ｜ 2026-10-14 11:35:16 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="118.5" customHeight="1" s="17">
-      <c r="A14" s="9" t="inlineStr">
+    <row r="16" ht="196.05" customHeight="1" s="17">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>调整报告页面命名与日报日期筛选
 - 页面更名：KFM选冶厂月报UI Enhance → KFM月报UIE、KFM选冶厂月报 → KFM月报
@@ -2511,15 +2548,15 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="19.95" customHeight="1" s="17">
-      <c r="A15" s="8" t="inlineStr">
+    <row r="17" ht="19.95" customHeight="1" s="17">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>提交 630c17f ｜ 2026-10-14 10:06:29 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="196.05" customHeight="1" s="17">
-      <c r="A16" s="9" t="inlineStr">
+    <row r="18" ht="118.5" customHeight="1" s="17">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>更新语义模型分析报告：同步本轮修复
 - 同步年累计完成L1 新口径与新增参数、中间表变化
@@ -2529,15 +2566,15 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="19.95" customHeight="1" s="17">
-      <c r="A17" s="8" t="inlineStr">
+    <row r="19" ht="19.95" customHeight="1" s="17">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>提交 1794160 ｜ 2026-10-14 10:06:24 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="118.5" customHeight="1" s="17">
-      <c r="A18" s="9" t="inlineStr">
+    <row r="20" ht="87.45" customHeight="1" s="17">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>调整报告视觉对象布局与筛选
 - 按钮/书签视觉对象位置与尺寸微调
@@ -2547,15 +2584,15 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="19.95" customHeight="1" s="17">
-      <c r="A19" s="8" t="inlineStr">
+    <row r="21" ht="19.95" customHeight="1" s="17">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>提交 9cbf408 ｜ 2026-10-14 10:06:18 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="87.45" customHeight="1" s="17">
-      <c r="A20" s="9" t="inlineStr">
+    <row r="22" ht="103.05" customHeight="1" s="17">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>修复语义模型分析报告发现的问题
 - 年累计完成L1 口径修正：累计预测数 → 累计实际数（新增列，经上月编码关联月报），消除重复计算
@@ -2570,15 +2607,15 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="19.95" customHeight="1" s="17">
-      <c r="A21" s="8" t="inlineStr">
+    <row r="23" ht="19.95" customHeight="1" s="17">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>提交 07f180b ｜ 2026-10-14 07:21:58 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="103.05" customHeight="1" s="17">
-      <c r="A22" s="9" t="inlineStr">
+    <row r="24" ht="118.5" customHeight="1" s="17">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>修正日报度量值：清理标题围栏并调整年累计完成字段
 - 标题-日报：移除多余的三反引号围栏标记，修复 TMDL 语法解析
@@ -2588,15 +2625,15 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="19.95" customHeight="1" s="17">
-      <c r="A23" s="8" t="inlineStr">
+    <row r="25" ht="19.95" customHeight="1" s="17">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>提交 2d4f16f ｜ 2026-10-14 07:01:02 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="118.5" customHeight="1" s="17">
-      <c r="A24" s="9" t="inlineStr">
+    <row r="26" ht="87.45" customHeight="1" s="17">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>新增 KFM日月报语义模型分析报告
 HTML 分析报告，涵盖模型总览、M 转换逻辑、DAX 计算逻辑与分级问题清单。
@@ -2604,15 +2641,15 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="19.95" customHeight="1" s="17">
-      <c r="A25" s="8" t="inlineStr">
+    <row r="27" ht="19.95" customHeight="1" s="17">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>提交 5ba71b7 ｜ 2026-10-14 06:57:45 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="87.45" customHeight="1" s="17">
-      <c r="A26" s="9" t="inlineStr">
+    <row r="28" ht="87.45" customHeight="1" s="17">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>修正 DAX/M 代码注释，准确反映实际逻辑
 - functions.tmdl：修正 FormatAmount/FormatRatio 的格式注释（两位小数/差额/百分比），SameMonthPriorYear 顶部注释去掉「年累计实际数」限定
@@ -2621,15 +2658,15 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="19.95" customHeight="1" s="17">
-      <c r="A27" s="8" t="inlineStr">
+    <row r="29" ht="19.95" customHeight="1" s="17">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t>提交 cea3882 ｜ 2026-10-14 06:34:36 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="87.45" customHeight="1" s="17">
-      <c r="A28" s="9" t="inlineStr">
+    <row r="30" ht="103.05" customHeight="1" s="17">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>优化语义模型自定义函数命名
 - FormatKFM → FormatAmount（数量格式）
@@ -2639,15 +2676,15 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="19.95" customHeight="1" s="17">
-      <c r="A29" s="8" t="inlineStr">
+    <row r="31" ht="19.95" customHeight="1" s="17">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>提交 9f32794 ｜ 2026-10-14 06:22:46 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="103.05" customHeight="1" s="17">
-      <c r="A30" s="9" t="inlineStr">
+    <row r="32" ht="133.95" customHeight="1" s="17">
+      <c r="A32" s="9" t="inlineStr">
         <is>
           <t>重命名报表项目：KFM选冶厂月报 → L3报表-KFM日月报
 删除旧项目文件，改用新项目名称。
@@ -2655,15 +2692,15 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="19.95" customHeight="1" s="17">
-      <c r="A31" s="8" t="inlineStr">
+    <row r="33" ht="19.95" customHeight="1" s="17">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>提交 07301c6 ｜ 2026-10-13 19:57:45 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="133.95" customHeight="1" s="17">
-      <c r="A32" s="9" t="inlineStr">
+    <row r="34" ht="133.95" customHeight="1" s="17">
+      <c r="A34" s="9" t="inlineStr">
         <is>
           <t>修复 KFM选冶厂月报 TMDL 缩进错误
 将 source 的 M 代码改为三反引号形式，修复 let 顶格导致的 TMDL 缩进解析错误。
@@ -2671,15 +2708,15 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="19.95" customHeight="1" s="17">
-      <c r="A33" s="8" t="inlineStr">
+    <row r="35" ht="19.95" customHeight="1" s="17">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>提交 1485d55 ｜ 2026-10-13 19:45:55 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="133.95" customHeight="1" s="17">
-      <c r="A34" s="9" t="inlineStr">
+    <row r="36" ht="273.45" customHeight="1" s="17">
+      <c r="A36" s="9" t="inlineStr">
         <is>
           <t>优化全部 M 查询：步骤名语义化与步骤合并
 - KFM选冶厂月报：Cube.Transform 直接输出最终列名，删除「重命名列」「新增指标项列」步骤；去掉未使用的产品、矿坑、指标编码维度；合并类别2分组逻辑与最近月份计算；步骤名统一中文
@@ -2688,15 +2725,15 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="19.95" customHeight="1" s="17">
-      <c r="A35" s="8" t="inlineStr">
+    <row r="37" ht="19.95" customHeight="1" s="17">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>提交 6b4084c ｜ 2026-10-13 19:31:50 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="273.45" customHeight="1" s="17">
-      <c r="A36" s="9" t="inlineStr">
+    <row r="38" ht="56.55" customHeight="1" s="17">
+      <c r="A38" s="9" t="inlineStr">
         <is>
           <t>优化L1-KFM日报 M 查询：命名注释与步骤精简
 - Cube.Transform 直接输出最终列名，删除冗余的「重命名的列」步骤
@@ -2707,15 +2744,15 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="19.95" customHeight="1" s="17">
-      <c r="A37" s="8" t="inlineStr">
+    <row r="39" ht="19.95" customHeight="1" s="17">
+      <c r="A39" s="8" t="inlineStr">
         <is>
           <t>提交 2a59e2f ｜ 2026-10-13 19:15:18 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="56.55" customHeight="1" s="17">
-      <c r="A38" s="9" t="inlineStr">
+    <row r="40" ht="409.6" customHeight="1" s="17">
+      <c r="A40" s="9" t="inlineStr">
         <is>
           <t>优化L1-KFM日报 M 查询：内联两个中间表
 - 将 全年预算表、月累计预测表 两个中间表 expression 内联进 L1-KFM日报 的 M 查询，消除跨查询依赖
@@ -2726,15 +2763,15 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="19.95" customHeight="1" s="17">
-      <c r="A39" s="8" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="8" t="inlineStr">
         <is>
           <t>提交 48112a2 ｜ 2026-10-13 18:55:27 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="409.6" customHeight="1" s="17">
-      <c r="A40" s="9" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="9" t="inlineStr">
         <is>
           <t>升级语义模型兼容级别1702，新增日报模型与DAX函数(UDF)
 语义模型
@@ -2753,30 +2790,30 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="8" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="8" t="inlineStr">
         <is>
           <t>提交 69bb2ba ｜ 2026-10-13 01:42:09 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="9" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="9" t="inlineStr">
         <is>
           <t>新增项目版本信息 Excel 文档（含项目概述、Git版本历史、提交备注）
 Co-Authored-By: Claude Fable 5.1 &lt;noreply@anthropic.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="8" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
         <is>
           <t>提交 248840e ｜ 2026-10-13 01:07:27 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="9" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="9" t="inlineStr">
         <is>
           <t>初始化存档：KFM选冶厂月报 Power BI 项目（PBIP）
 项目概述
@@ -3016,13 +3053,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{02B32B95-2E6E-4435-B751-86B8FD913EDD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{637A9716-837B-4F7D-9AAF-DAA01F55DC69}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73E0F6B6-9504-42BE-A47E-66B81F16B99D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4FD47A7-35B7-41E9-BBFE-A01A82E5D438}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54739EE9-52E6-4210-99DF-0EEB50353E6F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F55CCBAD-B891-4114-92B1-F8CD79EBB7A5}"/>
 </file>
--- a/L3报表项目版本信息.xlsx
+++ b/L3报表项目版本信息.xlsx
@@ -1088,7 +1088,7 @@
     <row r="32" ht="14.7" customHeight="1" s="17">
       <c r="A32" s="16" t="inlineStr">
         <is>
-          <t>映射表（各 6 列）：日报指标映射、月报指标映射</t>
+          <t>映射表：日报指标映射（6 列）、月报指标映射（7 列，含指标类别）</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
     <row r="34" ht="34.95" customHeight="1" s="17">
       <c r="A34" s="16" t="inlineStr">
         <is>
-          <t>度量值表（28 个度量值）</t>
+          <t>度量值表（27 个度量值）</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
     <row r="36" ht="19.5" customHeight="1" s="17">
       <c r="A36" s="23" t="inlineStr">
         <is>
-          <t>日报度量（8 个）：日完成、月累计、月计划L1、月比计划L1、年计划L1、年累计完成L1、年比计划L1、年累计完成L1_v2</t>
+          <t>日报度量（7 个）：日完成、月累计、月计划L1、月比计划L1、年计划L1、年比计划L1、年累计完成L1</t>
         </is>
       </c>
       <c r="B36" s="14" t="n"/>
@@ -1138,7 +1138,7 @@
     <row r="37" ht="22.05" customHeight="1" s="17">
       <c r="A37" s="23" t="inlineStr">
         <is>
-          <t>入选品位度量（4 个）：v钴入矿品位_新口径、v铜入矿品位_新口径、v铜回收率_新口径、v_钴回收率_新口径</t>
+          <t>新口径度量（4 个）：v钴入矿品位_新口径、v铜入矿品位_新口径、v_铜回收率_新口径、v_钴回收率_新口径</t>
         </is>
       </c>
       <c r="B37" s="14" t="n"/>
@@ -1169,7 +1169,7 @@
     <row r="40">
       <c r="A40" s="21" t="inlineStr">
         <is>
-          <t>Power Query 参数：p_月报起始日期=2025-01-01、p_日报起始日期=2026-01-01、服务器/系统编号/客户端ID/SharePoint站点（中间表 全年预算表、月累计实际表 已内联进 L1-KFM日报）</t>
+          <t>Power Query 参数：p_月报起始日期=2025-01-01、p_日报起始日期=2026-01-01、服务器=10.43.11.32 / 系统编号=00 / 客户端ID=100 / SharePoint站点=https://cmocco.sharepoint.com/teams/PBI/</t>
         </is>
       </c>
       <c r="B40" s="14" t="n"/>
@@ -1234,7 +1234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="5" customWidth="1" style="17" min="1" max="1"/>
@@ -1312,17 +1312,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3383b89</t>
+          <t>bb50397</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3383b89a26c058fe8288116492857b5876884703</t>
+          <t>bb5039713a0cb6d622ad399c3d5e0a4892ad9f8b</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-10-15 10:27:59</t>
+          <t>2026-10-15 16:30:36</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>度量值显示文件夹加数字前缀排序并改名新口径</t>
+          <t>切换数据源并重构回收率为量×率新口径，合并度量值</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1346,13 +1346,13 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="J2" t="n">
-        <v>56</v>
+        <v>558</v>
       </c>
       <c r="K2" t="n">
-        <v>58</v>
+        <v>445</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" s="17">
@@ -1361,96 +1361,96 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>3383b89</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>3383b89a26c058fe8288116492857b5876884703</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-10-15 10:27:59</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>度量值显示文件夹加数字前缀排序并改名新口径</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>7</v>
+      </c>
+      <c r="J3" t="n">
+        <v>56</v>
+      </c>
+      <c r="K3" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1" s="17">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>03b7f44</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>03b7f44d157dc79e23a7b3cd8c6f93bbdc3b36a4</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>2026-10-15 10:05:16</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Jevon Zhu</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>jevonzhu2008@gmail.com</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>二级指标列改名与入选品位/回收率新口径，同步报表与分析报告</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="I3" t="n">
+      <c r="I4" t="n">
         <v>34</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J4" t="n">
         <v>348</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K4" t="n">
         <v>10809</v>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1" s="17">
-      <c r="A4" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>6e604e4</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>6e604e4d0315cd3426b5f37097aed19041b27654</t>
-        </is>
-      </c>
-      <c r="D4" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-14 18:41:35</t>
-        </is>
-      </c>
-      <c r="E4" s="13" t="inlineStr">
-        <is>
-          <t>Jevon Zhu</t>
-        </is>
-      </c>
-      <c r="F4" s="13" t="inlineStr">
-        <is>
-          <t>jevonzhu2008@gmail.com</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>日报表新增入选品位度量值与指标列，同步月报口径、报表页面与分析报告</t>
-        </is>
-      </c>
-      <c r="H4" s="13" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="I4" s="13" t="n">
-        <v>18</v>
-      </c>
-      <c r="J4" s="13" t="n">
-        <v>1565</v>
-      </c>
-      <c r="K4" s="13" t="n">
-        <v>175</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" s="17">
@@ -1459,17 +1459,17 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>d6b1785</t>
+          <t>6e604e4</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>d6b1785b86f19f2db61866bfc840abcac3e1f2cf</t>
+          <t>6e604e4d0315cd3426b5f37097aed19041b27654</t>
         </is>
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>2026-10-14 14:05:13</t>
+          <t>2026-10-14 18:41:35</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>重命名报表项目：L3报表-KFM日月报 → L3报表</t>
+          <t>日报表新增入选品位度量值与指标列，同步月报口径、报表页面与分析报告</t>
         </is>
       </c>
       <c r="H5" s="13" t="inlineStr">
@@ -1493,13 +1493,13 @@
         </is>
       </c>
       <c r="I5" s="13" t="n">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="J5" s="13" t="n">
-        <v>23</v>
+        <v>1565</v>
       </c>
       <c r="K5" s="13" t="n">
-        <v>17</v>
+        <v>175</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" s="17">
@@ -1508,879 +1508,928 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
+          <t>d6b1785</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>d6b1785b86f19f2db61866bfc840abcac3e1f2cf</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-14 14:05:13</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F6" s="13" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>重命名报表项目：L3报表-KFM日月报 → L3报表</t>
+        </is>
+      </c>
+      <c r="H6" s="13" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I6" s="13" t="n">
+        <v>68</v>
+      </c>
+      <c r="J6" s="13" t="n">
+        <v>23</v>
+      </c>
+      <c r="K6" s="13" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1" s="17">
+      <c r="A7" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
           <t>8c90e31</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>8c90e3154248a749ec3ef3bc61d68576b709d2f7</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t>2026-10-14 12:08:57</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E7" s="13" t="inlineStr">
         <is>
           <t>Jevon Zhu</t>
         </is>
       </c>
-      <c r="F6" s="13" t="inlineStr">
+      <c r="F7" s="13" t="inlineStr">
         <is>
           <t>jevonzhu2008@gmail.com</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>更新语义模型分析报告：同步 M 优化与列精简</t>
         </is>
       </c>
-      <c r="H6" s="13" t="inlineStr">
+      <c r="H7" s="13" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="I6" s="13" t="n">
+      <c r="I7" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="J6" s="13" t="n">
+      <c r="J7" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="K6" s="13" t="n">
+      <c r="K7" s="13" t="n">
         <v>16</v>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1" s="17">
-      <c r="A7" s="18" t="n">
+    <row r="8" ht="30" customHeight="1" s="17">
+      <c r="A8" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>7148b64</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>7148b64ddd4ee32a7c06e2f912d939dc2ba4e1b5</t>
+        </is>
+      </c>
+      <c r="D8" s="18" t="inlineStr">
+        <is>
+          <t>2026-10-14 11:35:22</t>
+        </is>
+      </c>
+      <c r="E8" s="18" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F8" s="18" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>优化语义模型 M 代码与输出列</t>
+        </is>
+      </c>
+      <c r="H8" s="18" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I8" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="J8" s="18" t="n">
+        <v>38</v>
+      </c>
+      <c r="K8" s="18" t="n">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1" s="17">
+      <c r="A9" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>f996ae9</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>f996ae982e67b13a495117c8a9b34531f4eded82</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-14 11:35:16</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>调整报告页面命名与日报日期筛选</t>
+        </is>
+      </c>
+      <c r="H9" s="13" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I9" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>7148b64</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>7148b64ddd4ee32a7c06e2f912d939dc2ba4e1b5</t>
-        </is>
-      </c>
-      <c r="D7" s="18" t="inlineStr">
-        <is>
-          <t>2026-10-14 11:35:22</t>
-        </is>
-      </c>
-      <c r="E7" s="18" t="inlineStr">
+      <c r="J9" s="13" t="n">
+        <v>133</v>
+      </c>
+      <c r="K9" s="13" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1" s="17">
+      <c r="A10" s="18" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="18" t="inlineStr">
+        <is>
+          <t>630c17f</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>630c17fceaf47b46c21633e044fda78155ac0443</t>
+        </is>
+      </c>
+      <c r="D10" s="18" t="inlineStr">
+        <is>
+          <t>2026-10-14 10:06:29</t>
+        </is>
+      </c>
+      <c r="E10" s="18" t="inlineStr">
         <is>
           <t>Jevon Zhu</t>
         </is>
       </c>
-      <c r="F7" s="18" t="inlineStr">
+      <c r="F10" s="18" t="inlineStr">
         <is>
           <t>jevonzhu2008@gmail.com</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>优化语义模型 M 代码与输出列</t>
-        </is>
-      </c>
-      <c r="H7" s="18" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>更新语义模型分析报告：同步本轮修复</t>
+        </is>
+      </c>
+      <c r="H10" s="18" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="I7" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="J7" s="18" t="n">
-        <v>38</v>
-      </c>
-      <c r="K7" s="18" t="n">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1" s="17">
-      <c r="A8" s="13" t="n">
+      <c r="I10" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="18" t="n">
+        <v>35</v>
+      </c>
+      <c r="K10" s="18" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1" s="17">
+      <c r="A11" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>1794160</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>179416093e3aff5472f3a2f4719d2270cff850d1</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-14 10:06:24</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F11" s="13" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>调整报告视觉对象布局与筛选</t>
+        </is>
+      </c>
+      <c r="H11" s="13" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I11" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>f996ae9</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>f996ae982e67b13a495117c8a9b34531f4eded82</t>
-        </is>
-      </c>
-      <c r="D8" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-14 11:35:16</t>
-        </is>
-      </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="J11" s="13" t="n">
+        <v>37</v>
+      </c>
+      <c r="K11" s="13" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1" s="17">
+      <c r="A12" s="18" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="18" t="inlineStr">
+        <is>
+          <t>9cbf408</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>9cbf408d9186e1be6583b91b3e445288720dab30</t>
+        </is>
+      </c>
+      <c r="D12" s="18" t="inlineStr">
+        <is>
+          <t>2026-10-14 10:06:18</t>
+        </is>
+      </c>
+      <c r="E12" s="18" t="inlineStr">
         <is>
           <t>Jevon Zhu</t>
         </is>
       </c>
-      <c r="F8" s="13" t="inlineStr">
+      <c r="F12" s="18" t="inlineStr">
         <is>
           <t>jevonzhu2008@gmail.com</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>调整报告页面命名与日报日期筛选</t>
-        </is>
-      </c>
-      <c r="H8" s="13" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>修复语义模型分析报告发现的问题</t>
+        </is>
+      </c>
+      <c r="H12" s="18" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="I8" s="13" t="n">
+      <c r="I12" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="J12" s="18" t="n">
+        <v>86</v>
+      </c>
+      <c r="K12" s="18" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1" s="17">
+      <c r="A13" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>07f180b</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>07f180b9740c0c72f4ff4cb637acce0c8b718efc</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-14 07:21:58</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>修正日报度量值：清理标题围栏并调整年累计完成字段</t>
+        </is>
+      </c>
+      <c r="H13" s="13" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I13" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="K13" s="13" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1" s="17">
+      <c r="A14" s="18" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="18" t="inlineStr">
+        <is>
+          <t>2d4f16f</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>2d4f16fda737382909dd93ca2b175b6618fcbb57</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="inlineStr">
+        <is>
+          <t>2026-10-14 07:01:02</t>
+        </is>
+      </c>
+      <c r="E14" s="18" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F14" s="18" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>新增 KFM日月报语义模型分析报告</t>
+        </is>
+      </c>
+      <c r="H14" s="18" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I14" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" s="18" t="n">
+        <v>320</v>
+      </c>
+      <c r="K14" s="18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1" s="17">
+      <c r="A15" s="13" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>5ba71b7</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>5ba71b7bdd8c9fa3140791e2c325425796229e13</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-14 06:57:45</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F15" s="13" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>修正 DAX/M 代码注释，准确反映实际逻辑</t>
+        </is>
+      </c>
+      <c r="H15" s="13" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I15" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="J15" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="K15" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="J8" s="13" t="n">
-        <v>133</v>
-      </c>
-      <c r="K8" s="13" t="n">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1" s="17">
-      <c r="A9" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>630c17f</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>630c17fceaf47b46c21633e044fda78155ac0443</t>
-        </is>
-      </c>
-      <c r="D9" s="18" t="inlineStr">
-        <is>
-          <t>2026-10-14 10:06:29</t>
-        </is>
-      </c>
-      <c r="E9" s="18" t="inlineStr">
+    </row>
+    <row r="16" ht="30" customHeight="1" s="17">
+      <c r="A16" s="18" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="18" t="inlineStr">
+        <is>
+          <t>cea3882</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>cea3882903b1e0ebd284ee0a2acadb18380ddd7f</t>
+        </is>
+      </c>
+      <c r="D16" s="18" t="inlineStr">
+        <is>
+          <t>2026-10-14 06:34:36</t>
+        </is>
+      </c>
+      <c r="E16" s="18" t="inlineStr">
         <is>
           <t>Jevon Zhu</t>
         </is>
       </c>
-      <c r="F9" s="18" t="inlineStr">
+      <c r="F16" s="18" t="inlineStr">
         <is>
           <t>jevonzhu2008@gmail.com</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>更新语义模型分析报告：同步本轮修复</t>
-        </is>
-      </c>
-      <c r="H9" s="18" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>优化语义模型自定义函数命名</t>
+        </is>
+      </c>
+      <c r="H16" s="18" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="I9" s="18" t="n">
+      <c r="I16" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="J16" s="18" t="n">
+        <v>17</v>
+      </c>
+      <c r="K16" s="18" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1" s="17">
+      <c r="A17" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>9f32794</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>9f32794cc45bd00e695f720d0e38ca7eda0ee97d</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-14 06:22:46</t>
+        </is>
+      </c>
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F17" s="13" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>重命名报表项目：KFM选冶厂月报 → L3报表-KFM日月报</t>
+        </is>
+      </c>
+      <c r="H17" s="13" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I17" s="13" t="n">
+        <v>70</v>
+      </c>
+      <c r="J17" s="13" t="n">
+        <v>695</v>
+      </c>
+      <c r="K17" s="13" t="n">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1" s="17">
+      <c r="A18" s="18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="18" t="inlineStr">
+        <is>
+          <t>07301c6</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>07301c63639499dc1642f9abe29a9baee1e0c3cf</t>
+        </is>
+      </c>
+      <c r="D18" s="18" t="inlineStr">
+        <is>
+          <t>2026-10-13 19:57:45</t>
+        </is>
+      </c>
+      <c r="E18" s="18" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F18" s="18" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>修复 KFM选冶厂月报 TMDL 缩进错误</t>
+        </is>
+      </c>
+      <c r="H18" s="18" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I18" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="J9" s="18" t="n">
+      <c r="J18" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1" s="17">
+      <c r="A19" s="13" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>1485d55</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>1485d55c4d5b2c241eb05e9040a3897476085331</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-13 19:45:55</t>
+        </is>
+      </c>
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>优化全部 M 查询：步骤名语义化与步骤合并</t>
+        </is>
+      </c>
+      <c r="H19" s="13" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I19" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="J19" s="13" t="n">
+        <v>134</v>
+      </c>
+      <c r="K19" s="13" t="n">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1" s="17">
+      <c r="A20" s="18" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="18" t="inlineStr">
+        <is>
+          <t>6b4084c</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>6b4084c9a3fb078c53fcbdd2549a2adc1fc7d100</t>
+        </is>
+      </c>
+      <c r="D20" s="18" t="inlineStr">
+        <is>
+          <t>2026-10-13 19:31:50</t>
+        </is>
+      </c>
+      <c r="E20" s="18" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F20" s="18" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>优化L1-KFM日报 M 查询：命名注释与步骤精简</t>
+        </is>
+      </c>
+      <c r="H20" s="18" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I20" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" s="18" t="n">
+        <v>130</v>
+      </c>
+      <c r="K20" s="18" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>2a59e2f</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>2a59e2f68de3a82d02c6493c75d4a170ce013fae</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-13 19:15:18</t>
+        </is>
+      </c>
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F21" s="13" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>优化L1-KFM日报 M 查询：内联两个中间表</t>
+        </is>
+      </c>
+      <c r="H21" s="13" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I21" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="J21" s="13" t="n">
+        <v>21</v>
+      </c>
+      <c r="K21" s="13" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="18" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="18" t="inlineStr">
+        <is>
+          <t>48112a2</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>48112a2bfe1b2809ef94fe779a2e7a6c65d60bb2</t>
+        </is>
+      </c>
+      <c r="D22" s="18" t="inlineStr">
+        <is>
+          <t>2026-10-13 18:55:27</t>
+        </is>
+      </c>
+      <c r="E22" s="18" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F22" s="18" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>升级语义模型兼容级别1702，新增日报模型与DAX函数(UDF)</t>
+        </is>
+      </c>
+      <c r="H22" s="18" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I22" s="18" t="n">
         <v>35</v>
       </c>
-      <c r="K9" s="18" t="n">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1" s="17">
-      <c r="A10" s="13" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>1794160</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>179416093e3aff5472f3a2f4719d2270cff850d1</t>
-        </is>
-      </c>
-      <c r="D10" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-14 10:06:24</t>
-        </is>
-      </c>
-      <c r="E10" s="13" t="inlineStr">
+      <c r="J22" s="18" t="n">
+        <v>5662</v>
+      </c>
+      <c r="K22" s="18" t="n">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>69bb2ba</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>69bb2ba9dc7aa839a00235f2ef0ed1b691d7384e</t>
+        </is>
+      </c>
+      <c r="D23" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-13 01:42:09</t>
+        </is>
+      </c>
+      <c r="E23" s="13" t="inlineStr">
         <is>
           <t>Jevon Zhu</t>
         </is>
       </c>
-      <c r="F10" s="13" t="inlineStr">
+      <c r="F23" s="13" t="inlineStr">
         <is>
           <t>jevonzhu2008@gmail.com</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>调整报告视觉对象布局与筛选</t>
-        </is>
-      </c>
-      <c r="H10" s="13" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>新增项目版本信息 Excel 文档（含项目概述、Git版本历史、提交备注）</t>
+        </is>
+      </c>
+      <c r="H23" s="13" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="I10" s="13" t="n">
-        <v>7</v>
-      </c>
-      <c r="J10" s="13" t="n">
-        <v>37</v>
-      </c>
-      <c r="K10" s="13" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1" s="17">
-      <c r="A11" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>9cbf408</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>9cbf408d9186e1be6583b91b3e445288720dab30</t>
-        </is>
-      </c>
-      <c r="D11" s="18" t="inlineStr">
-        <is>
-          <t>2026-10-14 10:06:18</t>
-        </is>
-      </c>
-      <c r="E11" s="18" t="inlineStr">
+      <c r="I23" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="18" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="18" t="inlineStr">
+        <is>
+          <t>248840e</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>248840e9d232eacba69832ed5401065fb3ce1cab</t>
+        </is>
+      </c>
+      <c r="D24" s="18" t="inlineStr">
+        <is>
+          <t>2026-10-13 01:07:27</t>
+        </is>
+      </c>
+      <c r="E24" s="18" t="inlineStr">
         <is>
           <t>Jevon Zhu</t>
         </is>
       </c>
-      <c r="F11" s="18" t="inlineStr">
+      <c r="F24" s="18" t="inlineStr">
         <is>
           <t>jevonzhu2008@gmail.com</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>修复语义模型分析报告发现的问题</t>
-        </is>
-      </c>
-      <c r="H11" s="18" t="inlineStr">
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>初始化存档：KFM选冶厂月报 Power BI 项目（PBIP）</t>
+        </is>
+      </c>
+      <c r="H24" s="18" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="I11" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="J11" s="18" t="n">
-        <v>86</v>
-      </c>
-      <c r="K11" s="18" t="n">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1" s="17">
-      <c r="A12" s="13" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="13" t="inlineStr">
-        <is>
-          <t>07f180b</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>07f180b9740c0c72f4ff4cb637acce0c8b718efc</t>
-        </is>
-      </c>
-      <c r="D12" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-14 07:21:58</t>
-        </is>
-      </c>
-      <c r="E12" s="13" t="inlineStr">
-        <is>
-          <t>Jevon Zhu</t>
-        </is>
-      </c>
-      <c r="F12" s="13" t="inlineStr">
-        <is>
-          <t>jevonzhu2008@gmail.com</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>修正日报度量值：清理标题围栏并调整年累计完成字段</t>
-        </is>
-      </c>
-      <c r="H12" s="13" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="I12" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="K12" s="13" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1" s="17">
-      <c r="A13" s="18" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>2d4f16f</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>2d4f16fda737382909dd93ca2b175b6618fcbb57</t>
-        </is>
-      </c>
-      <c r="D13" s="18" t="inlineStr">
-        <is>
-          <t>2026-10-14 07:01:02</t>
-        </is>
-      </c>
-      <c r="E13" s="18" t="inlineStr">
-        <is>
-          <t>Jevon Zhu</t>
-        </is>
-      </c>
-      <c r="F13" s="18" t="inlineStr">
-        <is>
-          <t>jevonzhu2008@gmail.com</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>新增 KFM日月报语义模型分析报告</t>
-        </is>
-      </c>
-      <c r="H13" s="18" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="I13" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" s="18" t="n">
-        <v>320</v>
-      </c>
-      <c r="K13" s="18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1" s="17">
-      <c r="A14" s="13" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="13" t="inlineStr">
-        <is>
-          <t>5ba71b7</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>5ba71b7bdd8c9fa3140791e2c325425796229e13</t>
-        </is>
-      </c>
-      <c r="D14" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-14 06:57:45</t>
-        </is>
-      </c>
-      <c r="E14" s="13" t="inlineStr">
-        <is>
-          <t>Jevon Zhu</t>
-        </is>
-      </c>
-      <c r="F14" s="13" t="inlineStr">
-        <is>
-          <t>jevonzhu2008@gmail.com</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>修正 DAX/M 代码注释，准确反映实际逻辑</t>
-        </is>
-      </c>
-      <c r="H14" s="13" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="I14" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="J14" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="K14" s="13" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1" s="17">
-      <c r="A15" s="18" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>cea3882</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>cea3882903b1e0ebd284ee0a2acadb18380ddd7f</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>2026-10-14 06:34:36</t>
-        </is>
-      </c>
-      <c r="E15" s="18" t="inlineStr">
-        <is>
-          <t>Jevon Zhu</t>
-        </is>
-      </c>
-      <c r="F15" s="18" t="inlineStr">
-        <is>
-          <t>jevonzhu2008@gmail.com</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>优化语义模型自定义函数命名</t>
-        </is>
-      </c>
-      <c r="H15" s="18" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="I15" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="J15" s="18" t="n">
-        <v>17</v>
-      </c>
-      <c r="K15" s="18" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1" s="17">
-      <c r="A16" s="13" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="13" t="inlineStr">
-        <is>
-          <t>9f32794</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>9f32794cc45bd00e695f720d0e38ca7eda0ee97d</t>
-        </is>
-      </c>
-      <c r="D16" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-14 06:22:46</t>
-        </is>
-      </c>
-      <c r="E16" s="13" t="inlineStr">
-        <is>
-          <t>Jevon Zhu</t>
-        </is>
-      </c>
-      <c r="F16" s="13" t="inlineStr">
-        <is>
-          <t>jevonzhu2008@gmail.com</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>重命名报表项目：KFM选冶厂月报 → L3报表-KFM日月报</t>
-        </is>
-      </c>
-      <c r="H16" s="13" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="I16" s="13" t="n">
-        <v>70</v>
-      </c>
-      <c r="J16" s="13" t="n">
-        <v>695</v>
-      </c>
-      <c r="K16" s="13" t="n">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1" s="17">
-      <c r="A17" s="18" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>07301c6</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>07301c63639499dc1642f9abe29a9baee1e0c3cf</t>
-        </is>
-      </c>
-      <c r="D17" s="18" t="inlineStr">
-        <is>
-          <t>2026-10-13 19:57:45</t>
-        </is>
-      </c>
-      <c r="E17" s="18" t="inlineStr">
-        <is>
-          <t>Jevon Zhu</t>
-        </is>
-      </c>
-      <c r="F17" s="18" t="inlineStr">
-        <is>
-          <t>jevonzhu2008@gmail.com</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>修复 KFM选冶厂月报 TMDL 缩进错误</t>
-        </is>
-      </c>
-      <c r="H17" s="18" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="I17" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="K17" s="18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1" s="17">
-      <c r="A18" s="13" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="13" t="inlineStr">
-        <is>
-          <t>1485d55</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>1485d55c4d5b2c241eb05e9040a3897476085331</t>
-        </is>
-      </c>
-      <c r="D18" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-13 19:45:55</t>
-        </is>
-      </c>
-      <c r="E18" s="13" t="inlineStr">
-        <is>
-          <t>Jevon Zhu</t>
-        </is>
-      </c>
-      <c r="F18" s="13" t="inlineStr">
-        <is>
-          <t>jevonzhu2008@gmail.com</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>优化全部 M 查询：步骤名语义化与步骤合并</t>
-        </is>
-      </c>
-      <c r="H18" s="13" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="I18" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="J18" s="13" t="n">
-        <v>134</v>
-      </c>
-      <c r="K18" s="13" t="n">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1" s="17">
-      <c r="A19" s="18" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>6b4084c</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>6b4084c9a3fb078c53fcbdd2549a2adc1fc7d100</t>
-        </is>
-      </c>
-      <c r="D19" s="18" t="inlineStr">
-        <is>
-          <t>2026-10-13 19:31:50</t>
-        </is>
-      </c>
-      <c r="E19" s="18" t="inlineStr">
-        <is>
-          <t>Jevon Zhu</t>
-        </is>
-      </c>
-      <c r="F19" s="18" t="inlineStr">
-        <is>
-          <t>jevonzhu2008@gmail.com</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>优化L1-KFM日报 M 查询：命名注释与步骤精简</t>
-        </is>
-      </c>
-      <c r="H19" s="18" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="I19" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="J19" s="18" t="n">
-        <v>130</v>
-      </c>
-      <c r="K19" s="18" t="n">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="20" ht="30" customHeight="1" s="17">
-      <c r="A20" s="13" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="13" t="inlineStr">
-        <is>
-          <t>2a59e2f</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>2a59e2f68de3a82d02c6493c75d4a170ce013fae</t>
-        </is>
-      </c>
-      <c r="D20" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-13 19:15:18</t>
-        </is>
-      </c>
-      <c r="E20" s="13" t="inlineStr">
-        <is>
-          <t>Jevon Zhu</t>
-        </is>
-      </c>
-      <c r="F20" s="13" t="inlineStr">
-        <is>
-          <t>jevonzhu2008@gmail.com</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>优化L1-KFM日报 M 查询：内联两个中间表</t>
-        </is>
-      </c>
-      <c r="H20" s="13" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="I20" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="J20" s="13" t="n">
-        <v>21</v>
-      </c>
-      <c r="K20" s="13" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="18" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>48112a2</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>48112a2bfe1b2809ef94fe779a2e7a6c65d60bb2</t>
-        </is>
-      </c>
-      <c r="D21" s="18" t="inlineStr">
-        <is>
-          <t>2026-10-13 18:55:27</t>
-        </is>
-      </c>
-      <c r="E21" s="18" t="inlineStr">
-        <is>
-          <t>Jevon Zhu</t>
-        </is>
-      </c>
-      <c r="F21" s="18" t="inlineStr">
-        <is>
-          <t>jevonzhu2008@gmail.com</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>升级语义模型兼容级别1702，新增日报模型与DAX函数(UDF)</t>
-        </is>
-      </c>
-      <c r="H21" s="18" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="I21" s="18" t="n">
-        <v>35</v>
-      </c>
-      <c r="J21" s="18" t="n">
-        <v>5662</v>
-      </c>
-      <c r="K21" s="18" t="n">
-        <v>771</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="13" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="13" t="inlineStr">
-        <is>
-          <t>69bb2ba</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>69bb2ba9dc7aa839a00235f2ef0ed1b691d7384e</t>
-        </is>
-      </c>
-      <c r="D22" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-13 01:42:09</t>
-        </is>
-      </c>
-      <c r="E22" s="13" t="inlineStr">
-        <is>
-          <t>Jevon Zhu</t>
-        </is>
-      </c>
-      <c r="F22" s="13" t="inlineStr">
-        <is>
-          <t>jevonzhu2008@gmail.com</t>
-        </is>
-      </c>
-      <c r="G22" s="4" t="inlineStr">
-        <is>
-          <t>新增项目版本信息 Excel 文档（含项目概述、Git版本历史、提交备注）</t>
-        </is>
-      </c>
-      <c r="H22" s="13" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="I22" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="J22" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="18" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="18" t="inlineStr">
-        <is>
-          <t>248840e</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>248840e9d232eacba69832ed5401065fb3ce1cab</t>
-        </is>
-      </c>
-      <c r="D23" s="18" t="inlineStr">
-        <is>
-          <t>2026-10-13 01:07:27</t>
-        </is>
-      </c>
-      <c r="E23" s="18" t="inlineStr">
-        <is>
-          <t>Jevon Zhu</t>
-        </is>
-      </c>
-      <c r="F23" s="18" t="inlineStr">
-        <is>
-          <t>jevonzhu2008@gmail.com</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>初始化存档：KFM选冶厂月报 Power BI 项目（PBIP）</t>
-        </is>
-      </c>
-      <c r="H23" s="18" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="I23" s="18" t="n">
+      <c r="I24" s="18" t="n">
         <v>61</v>
       </c>
-      <c r="J23" s="18" t="n">
+      <c r="J24" s="18" t="n">
         <v>26750</v>
       </c>
-      <c r="K23" s="18" t="n">
+      <c r="K24" s="18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2395,7 +2444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A46"/>
+  <dimension ref="A1:A48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="19.95" customHeight="1"/>
   <cols>
     <col width="112" customWidth="1" style="17" min="1" max="1"/>
@@ -2418,12 +2467,32 @@
     <row r="3" ht="19.95" customHeight="1" s="17">
       <c r="A3" t="inlineStr">
         <is>
-          <t>提交 3383b89 ｜ 2026-10-15 10:27:59 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
+          <t>提交 bb50397 ｜ 2026-10-15 16:30:36 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
     <row r="4" ht="149.55" customHeight="1" s="17">
       <c r="A4" t="inlineStr">
+        <is>
+          <t>切换数据源并重构回收率为量×率新口径，合并度量值
+- 参数：SAP BW 服务器 10.43.11.32、系统编号 00、SharePoint 站点切至 cmocco/teams/PBI
+- 月报二级指标序号体系调整为 1004/1012/1013/1014/1015，月报映射补「指标类别」列（6→7）
+- 度量值：年累计完成L1_v2 并入 年累计完成L1（删除旧版），v铜回收率改名 v_铜回收率
+- 回收率改量×率加权反推新口径（浸出率/CCD洗涤效率），品位 ×100，ALLEXCEPT 保留日期筛选
+- 同步更新语义模型分析报告
+Co-Authored-By: Claude Opus 4.8 &lt;noreply@anthropic.com&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="19.95" customHeight="1" s="17">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>提交 3383b89 ｜ 2026-10-15 10:27:59 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="118.5" customHeight="1" s="17">
+      <c r="A6" t="inlineStr">
         <is>
           <t>度量值显示文件夹加数字前缀排序并改名新口径
 - 度量值 displayFolder 加数字前缀：00辅助 / 02月报 / 03日报，「入选品位」改名「01新口径」
@@ -2433,15 +2502,15 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="19.95" customHeight="1" s="17">
-      <c r="A5" t="inlineStr">
+    <row r="7" ht="19.95" customHeight="1" s="17">
+      <c r="A7" t="inlineStr">
         <is>
           <t>提交 03b7f44 ｜ 2026-10-15 10:05:16 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="118.5" customHeight="1" s="17">
-      <c r="A6" t="inlineStr">
+    <row r="8" ht="149.55" customHeight="1" s="17">
+      <c r="A8" t="inlineStr">
         <is>
           <t>二级指标列改名与入选品位/回收率新口径，同步报表与分析报告
 - 语义模型：「类别2」统一改名为「二级指标」，细分逻辑改按序号驱动；序号/排序/环节序号类型统一 int64
@@ -2452,15 +2521,15 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="19.95" customHeight="1" s="17">
-      <c r="A7" s="8" t="inlineStr">
+    <row r="9" ht="19.95" customHeight="1" s="17">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>提交 6e604e4 ｜ 2026-10-14 18:41:35 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="149.55" customHeight="1" s="17">
-      <c r="A8" s="9" t="inlineStr">
+    <row r="10" ht="133.95" customHeight="1" s="17">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>日报表新增入选品位度量值与指标列，同步月报口径、报表页面与分析报告
 - 日报表：新增「指标名称」「产品分类」两列，类别2/排序改按产品分类细分，输出列 15→17
@@ -2472,15 +2541,15 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="19.95" customHeight="1" s="17">
-      <c r="A9" s="8" t="inlineStr">
+    <row r="11" ht="19.95" customHeight="1" s="17">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>提交 d6b1785 ｜ 2026-10-14 14:05:13 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="133.95" customHeight="1" s="17">
-      <c r="A10" s="9" t="inlineStr">
+    <row r="12" ht="118.5" customHeight="1" s="17">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>重命名报表项目：L3报表-KFM日月报 → L3报表
 - 项目、报告、语义模型整体重命名为 L3报表（目录、.pbip、.platform、definition.pbir 同步更新）
@@ -2491,15 +2560,15 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="19.95" customHeight="1" s="17">
-      <c r="A11" s="8" t="inlineStr">
+    <row r="13" ht="19.95" customHeight="1" s="17">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>提交 8c90e31 ｜ 2026-10-14 12:08:57 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="118.5" customHeight="1" s="17">
-      <c r="A12" s="9" t="inlineStr">
+    <row r="14" ht="118.5" customHeight="1" s="17">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>更新语义模型分析报告：同步 M 优化与列精简
 - 模型总览列数同步：月报 18 列、日报 15 列
@@ -2509,15 +2578,15 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="19.95" customHeight="1" s="17">
-      <c r="A13" s="8" t="inlineStr">
+    <row r="15" ht="19.95" customHeight="1" s="17">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>提交 7148b64 ｜ 2026-10-14 11:35:22 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="118.5" customHeight="1" s="17">
-      <c r="A14" s="9" t="inlineStr">
+    <row r="16" ht="196.05" customHeight="1" s="17">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>优化语义模型 M 代码与输出列
 - 日报新增「日期筛选器」列（按「原矿处理量」最大标准日期标记「最近日期」）
@@ -2529,15 +2598,15 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="19.95" customHeight="1" s="17">
-      <c r="A15" s="8" t="inlineStr">
+    <row r="17" ht="19.95" customHeight="1" s="17">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>提交 f996ae9 ｜ 2026-10-14 11:35:16 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="196.05" customHeight="1" s="17">
-      <c r="A16" s="9" t="inlineStr">
+    <row r="18" ht="118.5" customHeight="1" s="17">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>调整报告页面命名与日报日期筛选
 - 页面更名：KFM选冶厂月报UI Enhance → KFM月报UIE、KFM选冶厂月报 → KFM月报
@@ -2548,15 +2617,15 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="19.95" customHeight="1" s="17">
-      <c r="A17" s="8" t="inlineStr">
+    <row r="19" ht="19.95" customHeight="1" s="17">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>提交 630c17f ｜ 2026-10-14 10:06:29 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="118.5" customHeight="1" s="17">
-      <c r="A18" s="9" t="inlineStr">
+    <row r="20" ht="87.45" customHeight="1" s="17">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>更新语义模型分析报告：同步本轮修复
 - 同步年累计完成L1 新口径与新增参数、中间表变化
@@ -2566,15 +2635,15 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="19.95" customHeight="1" s="17">
-      <c r="A19" s="8" t="inlineStr">
+    <row r="21" ht="19.95" customHeight="1" s="17">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>提交 1794160 ｜ 2026-10-14 10:06:24 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="87.45" customHeight="1" s="17">
-      <c r="A20" s="9" t="inlineStr">
+    <row r="22" ht="103.05" customHeight="1" s="17">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>调整报告视觉对象布局与筛选
 - 按钮/书签视觉对象位置与尺寸微调
@@ -2584,15 +2653,15 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="19.95" customHeight="1" s="17">
-      <c r="A21" s="8" t="inlineStr">
+    <row r="23" ht="19.95" customHeight="1" s="17">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>提交 9cbf408 ｜ 2026-10-14 10:06:18 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="103.05" customHeight="1" s="17">
-      <c r="A22" s="9" t="inlineStr">
+    <row r="24" ht="118.5" customHeight="1" s="17">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>修复语义模型分析报告发现的问题
 - 年累计完成L1 口径修正：累计预测数 → 累计实际数（新增列，经上月编码关联月报），消除重复计算
@@ -2607,15 +2676,15 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="19.95" customHeight="1" s="17">
-      <c r="A23" s="8" t="inlineStr">
+    <row r="25" ht="19.95" customHeight="1" s="17">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>提交 07f180b ｜ 2026-10-14 07:21:58 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="118.5" customHeight="1" s="17">
-      <c r="A24" s="9" t="inlineStr">
+    <row r="26" ht="87.45" customHeight="1" s="17">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>修正日报度量值：清理标题围栏并调整年累计完成字段
 - 标题-日报：移除多余的三反引号围栏标记，修复 TMDL 语法解析
@@ -2625,15 +2694,15 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="19.95" customHeight="1" s="17">
-      <c r="A25" s="8" t="inlineStr">
+    <row r="27" ht="19.95" customHeight="1" s="17">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>提交 2d4f16f ｜ 2026-10-14 07:01:02 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="87.45" customHeight="1" s="17">
-      <c r="A26" s="9" t="inlineStr">
+    <row r="28" ht="87.45" customHeight="1" s="17">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>新增 KFM日月报语义模型分析报告
 HTML 分析报告，涵盖模型总览、M 转换逻辑、DAX 计算逻辑与分级问题清单。
@@ -2641,15 +2710,15 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="19.95" customHeight="1" s="17">
-      <c r="A27" s="8" t="inlineStr">
+    <row r="29" ht="19.95" customHeight="1" s="17">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t>提交 5ba71b7 ｜ 2026-10-14 06:57:45 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="87.45" customHeight="1" s="17">
-      <c r="A28" s="9" t="inlineStr">
+    <row r="30" ht="103.05" customHeight="1" s="17">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>修正 DAX/M 代码注释，准确反映实际逻辑
 - functions.tmdl：修正 FormatAmount/FormatRatio 的格式注释（两位小数/差额/百分比），SameMonthPriorYear 顶部注释去掉「年累计实际数」限定
@@ -2658,15 +2727,15 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="19.95" customHeight="1" s="17">
-      <c r="A29" s="8" t="inlineStr">
+    <row r="31" ht="19.95" customHeight="1" s="17">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>提交 cea3882 ｜ 2026-10-14 06:34:36 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="103.05" customHeight="1" s="17">
-      <c r="A30" s="9" t="inlineStr">
+    <row r="32" ht="133.95" customHeight="1" s="17">
+      <c r="A32" s="9" t="inlineStr">
         <is>
           <t>优化语义模型自定义函数命名
 - FormatKFM → FormatAmount（数量格式）
@@ -2676,15 +2745,15 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="19.95" customHeight="1" s="17">
-      <c r="A31" s="8" t="inlineStr">
+    <row r="33" ht="19.95" customHeight="1" s="17">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>提交 9f32794 ｜ 2026-10-14 06:22:46 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="133.95" customHeight="1" s="17">
-      <c r="A32" s="9" t="inlineStr">
+    <row r="34" ht="133.95" customHeight="1" s="17">
+      <c r="A34" s="9" t="inlineStr">
         <is>
           <t>重命名报表项目：KFM选冶厂月报 → L3报表-KFM日月报
 删除旧项目文件，改用新项目名称。
@@ -2692,15 +2761,15 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="19.95" customHeight="1" s="17">
-      <c r="A33" s="8" t="inlineStr">
+    <row r="35" ht="19.95" customHeight="1" s="17">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>提交 07301c6 ｜ 2026-10-13 19:57:45 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="133.95" customHeight="1" s="17">
-      <c r="A34" s="9" t="inlineStr">
+    <row r="36" ht="273.45" customHeight="1" s="17">
+      <c r="A36" s="9" t="inlineStr">
         <is>
           <t>修复 KFM选冶厂月报 TMDL 缩进错误
 将 source 的 M 代码改为三反引号形式，修复 let 顶格导致的 TMDL 缩进解析错误。
@@ -2708,15 +2777,15 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="19.95" customHeight="1" s="17">
-      <c r="A35" s="8" t="inlineStr">
+    <row r="37" ht="19.95" customHeight="1" s="17">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>提交 1485d55 ｜ 2026-10-13 19:45:55 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="273.45" customHeight="1" s="17">
-      <c r="A36" s="9" t="inlineStr">
+    <row r="38" ht="56.55" customHeight="1" s="17">
+      <c r="A38" s="9" t="inlineStr">
         <is>
           <t>优化全部 M 查询：步骤名语义化与步骤合并
 - KFM选冶厂月报：Cube.Transform 直接输出最终列名，删除「重命名列」「新增指标项列」步骤；去掉未使用的产品、矿坑、指标编码维度；合并类别2分组逻辑与最近月份计算；步骤名统一中文
@@ -2725,15 +2794,15 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="19.95" customHeight="1" s="17">
-      <c r="A37" s="8" t="inlineStr">
+    <row r="39" ht="19.95" customHeight="1" s="17">
+      <c r="A39" s="8" t="inlineStr">
         <is>
           <t>提交 6b4084c ｜ 2026-10-13 19:31:50 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="56.55" customHeight="1" s="17">
-      <c r="A38" s="9" t="inlineStr">
+    <row r="40" ht="409.6" customHeight="1" s="17">
+      <c r="A40" s="9" t="inlineStr">
         <is>
           <t>优化L1-KFM日报 M 查询：命名注释与步骤精简
 - Cube.Transform 直接输出最终列名，删除冗余的「重命名的列」步骤
@@ -2744,15 +2813,15 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="19.95" customHeight="1" s="17">
-      <c r="A39" s="8" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="8" t="inlineStr">
         <is>
           <t>提交 2a59e2f ｜ 2026-10-13 19:15:18 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="409.6" customHeight="1" s="17">
-      <c r="A40" s="9" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="9" t="inlineStr">
         <is>
           <t>优化L1-KFM日报 M 查询：内联两个中间表
 - 将 全年预算表、月累计预测表 两个中间表 expression 内联进 L1-KFM日报 的 M 查询，消除跨查询依赖
@@ -2763,15 +2832,15 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="8" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="8" t="inlineStr">
         <is>
           <t>提交 48112a2 ｜ 2026-10-13 18:55:27 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="9" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="9" t="inlineStr">
         <is>
           <t>升级语义模型兼容级别1702，新增日报模型与DAX函数(UDF)
 语义模型
@@ -2790,30 +2859,30 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="8" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
         <is>
           <t>提交 69bb2ba ｜ 2026-10-13 01:42:09 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="9" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="9" t="inlineStr">
         <is>
           <t>新增项目版本信息 Excel 文档（含项目概述、Git版本历史、提交备注）
 Co-Authored-By: Claude Fable 5.1 &lt;noreply@anthropic.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="8" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="8" t="inlineStr">
         <is>
           <t>提交 248840e ｜ 2026-10-13 01:07:27 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="9" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="9" t="inlineStr">
         <is>
           <t>初始化存档：KFM选冶厂月报 Power BI 项目（PBIP）
 项目概述
@@ -2849,217 +2918,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" verticalDpi="0"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="文档" ma:contentTypeID="0x0101005D1433F41EF0D1478250392B90115F38" ma:contentTypeVersion="9" ma:contentTypeDescription="新建文档。" ma:contentTypeScope="" ma:versionID="032b99cbe0032f0cff5a48f1014b19a5">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c6652493-9e78-432e-96e9-9f560552d737" xmlns:ns3="81bdbfe7-c43e-4d85-9d9d-9a2adcba7e19" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="587c6ea9c9f887b9a4e3544120a7e33e" ns2:_="" ns3:_="">
-    <xsd:import namespace="c6652493-9e78-432e-96e9-9f560552d737"/>
-    <xsd:import namespace="81bdbfe7-c43e-4d85-9d9d-9a2adcba7e19"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="c6652493-9e78-432e-96e9-9f560552d737" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="图像标记" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="b2d6801b-f0bd-476f-bc0d-7adc71382b76" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="81bdbfe7-c43e-4d85-9d9d-9a2adcba7e19" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="14" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{8260f861-705f-495b-b301-6e45a48115a7}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="81bdbfe7-c43e-4d85-9d9d-9a2adcba7e19">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="内容类型"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="标题"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c6652493-9e78-432e-96e9-9f560552d737">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="81bdbfe7-c43e-4d85-9d9d-9a2adcba7e19" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{637A9716-837B-4F7D-9AAF-DAA01F55DC69}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4FD47A7-35B7-41E9-BBFE-A01A82E5D438}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F55CCBAD-B891-4114-92B1-F8CD79EBB7A5}"/>
 </file>
--- a/L3报表项目版本信息.xlsx
+++ b/L3报表项目版本信息.xlsx
@@ -1107,7 +1107,7 @@
     <row r="34" ht="34.95" customHeight="1" s="17">
       <c r="A34" s="16" t="inlineStr">
         <is>
-          <t>度量值表（27 个度量值）</t>
+          <t>度量值表（27 个度量值，全部带 /// 注释）</t>
         </is>
       </c>
     </row>
@@ -1234,7 +1234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="5" customWidth="1" style="17" min="1" max="1"/>
@@ -1312,17 +1312,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>bb50397</t>
+          <t>1d1d593</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>bb5039713a0cb6d622ad399c3d5e0a4892ad9f8b</t>
+          <t>1d1d593c545a179590a51490be65a752aa2f3419</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-10-15 16:30:36</t>
+          <t>2026-10-15 17:39:50</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>切换数据源并重构回收率为量×率新口径，合并度量值</t>
+          <t>修复度量值缺陷并为全部 27 个度量值补充注释，同步分析报告</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1346,13 +1346,13 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="J2" t="n">
-        <v>558</v>
+        <v>79</v>
       </c>
       <c r="K2" t="n">
-        <v>445</v>
+        <v>153</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" s="17">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3383b89</t>
+          <t>bb50397</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3383b89a26c058fe8288116492857b5876884703</t>
+          <t>bb5039713a0cb6d622ad399c3d5e0a4892ad9f8b</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-10-15 10:27:59</t>
+          <t>2026-10-15 16:30:36</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>度量值显示文件夹加数字前缀排序并改名新口径</t>
+          <t>切换数据源并重构回收率为量×率新口径，合并度量值</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1395,13 +1395,13 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="J3" t="n">
-        <v>56</v>
+        <v>558</v>
       </c>
       <c r="K3" t="n">
-        <v>58</v>
+        <v>445</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" s="17">
@@ -1410,96 +1410,96 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>3383b89</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>3383b89a26c058fe8288116492857b5876884703</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-10-15 10:27:59</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>度量值显示文件夹加数字前缀排序并改名新口径</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>7</v>
+      </c>
+      <c r="J4" t="n">
+        <v>56</v>
+      </c>
+      <c r="K4" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1" s="17">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>03b7f44</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>03b7f44d157dc79e23a7b3cd8c6f93bbdc3b36a4</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>2026-10-15 10:05:16</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Jevon Zhu</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>jevonzhu2008@gmail.com</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>二级指标列改名与入选品位/回收率新口径，同步报表与分析报告</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="I4" t="n">
+      <c r="I5" t="n">
         <v>34</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J5" t="n">
         <v>348</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K5" t="n">
         <v>10809</v>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1" s="17">
-      <c r="A5" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>6e604e4</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>6e604e4d0315cd3426b5f37097aed19041b27654</t>
-        </is>
-      </c>
-      <c r="D5" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-14 18:41:35</t>
-        </is>
-      </c>
-      <c r="E5" s="13" t="inlineStr">
-        <is>
-          <t>Jevon Zhu</t>
-        </is>
-      </c>
-      <c r="F5" s="13" t="inlineStr">
-        <is>
-          <t>jevonzhu2008@gmail.com</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>日报表新增入选品位度量值与指标列，同步月报口径、报表页面与分析报告</t>
-        </is>
-      </c>
-      <c r="H5" s="13" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="I5" s="13" t="n">
-        <v>18</v>
-      </c>
-      <c r="J5" s="13" t="n">
-        <v>1565</v>
-      </c>
-      <c r="K5" s="13" t="n">
-        <v>175</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" s="17">
@@ -1508,17 +1508,17 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>d6b1785</t>
+          <t>6e604e4</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>d6b1785b86f19f2db61866bfc840abcac3e1f2cf</t>
+          <t>6e604e4d0315cd3426b5f37097aed19041b27654</t>
         </is>
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>2026-10-14 14:05:13</t>
+          <t>2026-10-14 18:41:35</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>重命名报表项目：L3报表-KFM日月报 → L3报表</t>
+          <t>日报表新增入选品位度量值与指标列，同步月报口径、报表页面与分析报告</t>
         </is>
       </c>
       <c r="H6" s="13" t="inlineStr">
@@ -1542,13 +1542,13 @@
         </is>
       </c>
       <c r="I6" s="13" t="n">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="J6" s="13" t="n">
-        <v>23</v>
+        <v>1565</v>
       </c>
       <c r="K6" s="13" t="n">
-        <v>17</v>
+        <v>175</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" s="17">
@@ -1557,879 +1557,928 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
+          <t>d6b1785</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>d6b1785b86f19f2db61866bfc840abcac3e1f2cf</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-14 14:05:13</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>重命名报表项目：L3报表-KFM日月报 → L3报表</t>
+        </is>
+      </c>
+      <c r="H7" s="13" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I7" s="13" t="n">
+        <v>68</v>
+      </c>
+      <c r="J7" s="13" t="n">
+        <v>23</v>
+      </c>
+      <c r="K7" s="13" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1" s="17">
+      <c r="A8" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
           <t>8c90e31</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>8c90e3154248a749ec3ef3bc61d68576b709d2f7</t>
         </is>
       </c>
-      <c r="D7" s="13" t="inlineStr">
+      <c r="D8" s="13" t="inlineStr">
         <is>
           <t>2026-10-14 12:08:57</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E8" s="13" t="inlineStr">
         <is>
           <t>Jevon Zhu</t>
         </is>
       </c>
-      <c r="F7" s="13" t="inlineStr">
+      <c r="F8" s="13" t="inlineStr">
         <is>
           <t>jevonzhu2008@gmail.com</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>更新语义模型分析报告：同步 M 优化与列精简</t>
         </is>
       </c>
-      <c r="H7" s="13" t="inlineStr">
+      <c r="H8" s="13" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="I7" s="13" t="n">
+      <c r="I8" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="J7" s="13" t="n">
+      <c r="J8" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="K7" s="13" t="n">
+      <c r="K8" s="13" t="n">
         <v>16</v>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1" s="17">
-      <c r="A8" s="18" t="n">
+    <row r="9" ht="30" customHeight="1" s="17">
+      <c r="A9" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t>7148b64</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>7148b64ddd4ee32a7c06e2f912d939dc2ba4e1b5</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="inlineStr">
+        <is>
+          <t>2026-10-14 11:35:22</t>
+        </is>
+      </c>
+      <c r="E9" s="18" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F9" s="18" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>优化语义模型 M 代码与输出列</t>
+        </is>
+      </c>
+      <c r="H9" s="18" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I9" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="J9" s="18" t="n">
+        <v>38</v>
+      </c>
+      <c r="K9" s="18" t="n">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1" s="17">
+      <c r="A10" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>f996ae9</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>f996ae982e67b13a495117c8a9b34531f4eded82</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-14 11:35:16</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>调整报告页面命名与日报日期筛选</t>
+        </is>
+      </c>
+      <c r="H10" s="13" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I10" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="J10" s="13" t="n">
+        <v>133</v>
+      </c>
+      <c r="K10" s="13" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1" s="17">
+      <c r="A11" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t>630c17f</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>630c17fceaf47b46c21633e044fda78155ac0443</t>
+        </is>
+      </c>
+      <c r="D11" s="18" t="inlineStr">
+        <is>
+          <t>2026-10-14 10:06:29</t>
+        </is>
+      </c>
+      <c r="E11" s="18" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F11" s="18" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>更新语义模型分析报告：同步本轮修复</t>
+        </is>
+      </c>
+      <c r="H11" s="18" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I11" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="18" t="n">
+        <v>35</v>
+      </c>
+      <c r="K11" s="18" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1" s="17">
+      <c r="A12" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>1794160</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>179416093e3aff5472f3a2f4719d2270cff850d1</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-14 10:06:24</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F12" s="13" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>调整报告视觉对象布局与筛选</t>
+        </is>
+      </c>
+      <c r="H12" s="13" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I12" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>7148b64</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>7148b64ddd4ee32a7c06e2f912d939dc2ba4e1b5</t>
-        </is>
-      </c>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>2026-10-14 11:35:22</t>
-        </is>
-      </c>
-      <c r="E8" s="18" t="inlineStr">
+      <c r="J12" s="13" t="n">
+        <v>37</v>
+      </c>
+      <c r="K12" s="13" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1" s="17">
+      <c r="A13" s="18" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="18" t="inlineStr">
+        <is>
+          <t>9cbf408</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>9cbf408d9186e1be6583b91b3e445288720dab30</t>
+        </is>
+      </c>
+      <c r="D13" s="18" t="inlineStr">
+        <is>
+          <t>2026-10-14 10:06:18</t>
+        </is>
+      </c>
+      <c r="E13" s="18" t="inlineStr">
         <is>
           <t>Jevon Zhu</t>
         </is>
       </c>
-      <c r="F8" s="18" t="inlineStr">
+      <c r="F13" s="18" t="inlineStr">
         <is>
           <t>jevonzhu2008@gmail.com</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>优化语义模型 M 代码与输出列</t>
-        </is>
-      </c>
-      <c r="H8" s="18" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>修复语义模型分析报告发现的问题</t>
+        </is>
+      </c>
+      <c r="H13" s="18" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="I8" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="J8" s="18" t="n">
-        <v>38</v>
-      </c>
-      <c r="K8" s="18" t="n">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1" s="17">
-      <c r="A9" s="13" t="n">
+      <c r="I13" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>f996ae9</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>f996ae982e67b13a495117c8a9b34531f4eded82</t>
-        </is>
-      </c>
-      <c r="D9" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-14 11:35:16</t>
-        </is>
-      </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="J13" s="18" t="n">
+        <v>86</v>
+      </c>
+      <c r="K13" s="18" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1" s="17">
+      <c r="A14" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>07f180b</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>07f180b9740c0c72f4ff4cb637acce0c8b718efc</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-14 07:21:58</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="inlineStr">
         <is>
           <t>Jevon Zhu</t>
         </is>
       </c>
-      <c r="F9" s="13" t="inlineStr">
+      <c r="F14" s="13" t="inlineStr">
         <is>
           <t>jevonzhu2008@gmail.com</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>调整报告页面命名与日报日期筛选</t>
-        </is>
-      </c>
-      <c r="H9" s="13" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>修正日报度量值：清理标题围栏并调整年累计完成字段</t>
+        </is>
+      </c>
+      <c r="H14" s="13" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="I9" s="13" t="n">
+      <c r="I14" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="K14" s="13" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1" s="17">
+      <c r="A15" s="18" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="18" t="inlineStr">
+        <is>
+          <t>2d4f16f</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>2d4f16fda737382909dd93ca2b175b6618fcbb57</t>
+        </is>
+      </c>
+      <c r="D15" s="18" t="inlineStr">
+        <is>
+          <t>2026-10-14 07:01:02</t>
+        </is>
+      </c>
+      <c r="E15" s="18" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F15" s="18" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>新增 KFM日月报语义模型分析报告</t>
+        </is>
+      </c>
+      <c r="H15" s="18" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I15" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" s="18" t="n">
+        <v>320</v>
+      </c>
+      <c r="K15" s="18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1" s="17">
+      <c r="A16" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>5ba71b7</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>5ba71b7bdd8c9fa3140791e2c325425796229e13</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-14 06:57:45</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F16" s="13" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>修正 DAX/M 代码注释，准确反映实际逻辑</t>
+        </is>
+      </c>
+      <c r="H16" s="13" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I16" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="J16" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="K16" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="J9" s="13" t="n">
-        <v>133</v>
-      </c>
-      <c r="K9" s="13" t="n">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1" s="17">
-      <c r="A10" s="18" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>630c17f</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>630c17fceaf47b46c21633e044fda78155ac0443</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="inlineStr">
-        <is>
-          <t>2026-10-14 10:06:29</t>
-        </is>
-      </c>
-      <c r="E10" s="18" t="inlineStr">
+    </row>
+    <row r="17" ht="30" customHeight="1" s="17">
+      <c r="A17" s="18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="18" t="inlineStr">
+        <is>
+          <t>cea3882</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>cea3882903b1e0ebd284ee0a2acadb18380ddd7f</t>
+        </is>
+      </c>
+      <c r="D17" s="18" t="inlineStr">
+        <is>
+          <t>2026-10-14 06:34:36</t>
+        </is>
+      </c>
+      <c r="E17" s="18" t="inlineStr">
         <is>
           <t>Jevon Zhu</t>
         </is>
       </c>
-      <c r="F10" s="18" t="inlineStr">
+      <c r="F17" s="18" t="inlineStr">
         <is>
           <t>jevonzhu2008@gmail.com</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>更新语义模型分析报告：同步本轮修复</t>
-        </is>
-      </c>
-      <c r="H10" s="18" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>优化语义模型自定义函数命名</t>
+        </is>
+      </c>
+      <c r="H17" s="18" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="I10" s="18" t="n">
+      <c r="I17" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="J17" s="18" t="n">
+        <v>17</v>
+      </c>
+      <c r="K17" s="18" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1" s="17">
+      <c r="A18" s="13" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>9f32794</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>9f32794cc45bd00e695f720d0e38ca7eda0ee97d</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-14 06:22:46</t>
+        </is>
+      </c>
+      <c r="E18" s="13" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F18" s="13" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>重命名报表项目：KFM选冶厂月报 → L3报表-KFM日月报</t>
+        </is>
+      </c>
+      <c r="H18" s="13" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I18" s="13" t="n">
+        <v>70</v>
+      </c>
+      <c r="J18" s="13" t="n">
+        <v>695</v>
+      </c>
+      <c r="K18" s="13" t="n">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1" s="17">
+      <c r="A19" s="18" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="18" t="inlineStr">
+        <is>
+          <t>07301c6</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>07301c63639499dc1642f9abe29a9baee1e0c3cf</t>
+        </is>
+      </c>
+      <c r="D19" s="18" t="inlineStr">
+        <is>
+          <t>2026-10-13 19:57:45</t>
+        </is>
+      </c>
+      <c r="E19" s="18" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F19" s="18" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>修复 KFM选冶厂月报 TMDL 缩进错误</t>
+        </is>
+      </c>
+      <c r="H19" s="18" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I19" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="J10" s="18" t="n">
+      <c r="J19" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="K19" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1" s="17">
+      <c r="A20" s="13" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>1485d55</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>1485d55c4d5b2c241eb05e9040a3897476085331</t>
+        </is>
+      </c>
+      <c r="D20" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-13 19:45:55</t>
+        </is>
+      </c>
+      <c r="E20" s="13" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F20" s="13" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>优化全部 M 查询：步骤名语义化与步骤合并</t>
+        </is>
+      </c>
+      <c r="H20" s="13" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I20" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="J20" s="13" t="n">
+        <v>134</v>
+      </c>
+      <c r="K20" s="13" t="n">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="18" t="inlineStr">
+        <is>
+          <t>6b4084c</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>6b4084c9a3fb078c53fcbdd2549a2adc1fc7d100</t>
+        </is>
+      </c>
+      <c r="D21" s="18" t="inlineStr">
+        <is>
+          <t>2026-10-13 19:31:50</t>
+        </is>
+      </c>
+      <c r="E21" s="18" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F21" s="18" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>优化L1-KFM日报 M 查询：命名注释与步骤精简</t>
+        </is>
+      </c>
+      <c r="H21" s="18" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I21" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" s="18" t="n">
+        <v>130</v>
+      </c>
+      <c r="K21" s="18" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>2a59e2f</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>2a59e2f68de3a82d02c6493c75d4a170ce013fae</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-13 19:15:18</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F22" s="13" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>优化L1-KFM日报 M 查询：内联两个中间表</t>
+        </is>
+      </c>
+      <c r="H22" s="13" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I22" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="J22" s="13" t="n">
+        <v>21</v>
+      </c>
+      <c r="K22" s="13" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="18" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="18" t="inlineStr">
+        <is>
+          <t>48112a2</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>48112a2bfe1b2809ef94fe779a2e7a6c65d60bb2</t>
+        </is>
+      </c>
+      <c r="D23" s="18" t="inlineStr">
+        <is>
+          <t>2026-10-13 18:55:27</t>
+        </is>
+      </c>
+      <c r="E23" s="18" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F23" s="18" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>升级语义模型兼容级别1702，新增日报模型与DAX函数(UDF)</t>
+        </is>
+      </c>
+      <c r="H23" s="18" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I23" s="18" t="n">
         <v>35</v>
       </c>
-      <c r="K10" s="18" t="n">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1" s="17">
-      <c r="A11" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>1794160</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>179416093e3aff5472f3a2f4719d2270cff850d1</t>
-        </is>
-      </c>
-      <c r="D11" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-14 10:06:24</t>
-        </is>
-      </c>
-      <c r="E11" s="13" t="inlineStr">
+      <c r="J23" s="18" t="n">
+        <v>5662</v>
+      </c>
+      <c r="K23" s="18" t="n">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>69bb2ba</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>69bb2ba9dc7aa839a00235f2ef0ed1b691d7384e</t>
+        </is>
+      </c>
+      <c r="D24" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-13 01:42:09</t>
+        </is>
+      </c>
+      <c r="E24" s="13" t="inlineStr">
         <is>
           <t>Jevon Zhu</t>
         </is>
       </c>
-      <c r="F11" s="13" t="inlineStr">
+      <c r="F24" s="13" t="inlineStr">
         <is>
           <t>jevonzhu2008@gmail.com</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>调整报告视觉对象布局与筛选</t>
-        </is>
-      </c>
-      <c r="H11" s="13" t="inlineStr">
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>新增项目版本信息 Excel 文档（含项目概述、Git版本历史、提交备注）</t>
+        </is>
+      </c>
+      <c r="H24" s="13" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="I11" s="13" t="n">
-        <v>7</v>
-      </c>
-      <c r="J11" s="13" t="n">
-        <v>37</v>
-      </c>
-      <c r="K11" s="13" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1" s="17">
-      <c r="A12" s="18" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>9cbf408</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>9cbf408d9186e1be6583b91b3e445288720dab30</t>
-        </is>
-      </c>
-      <c r="D12" s="18" t="inlineStr">
-        <is>
-          <t>2026-10-14 10:06:18</t>
-        </is>
-      </c>
-      <c r="E12" s="18" t="inlineStr">
+      <c r="I24" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="18" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="18" t="inlineStr">
+        <is>
+          <t>248840e</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>248840e9d232eacba69832ed5401065fb3ce1cab</t>
+        </is>
+      </c>
+      <c r="D25" s="18" t="inlineStr">
+        <is>
+          <t>2026-10-13 01:07:27</t>
+        </is>
+      </c>
+      <c r="E25" s="18" t="inlineStr">
         <is>
           <t>Jevon Zhu</t>
         </is>
       </c>
-      <c r="F12" s="18" t="inlineStr">
+      <c r="F25" s="18" t="inlineStr">
         <is>
           <t>jevonzhu2008@gmail.com</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>修复语义模型分析报告发现的问题</t>
-        </is>
-      </c>
-      <c r="H12" s="18" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>初始化存档：KFM选冶厂月报 Power BI 项目（PBIP）</t>
+        </is>
+      </c>
+      <c r="H25" s="18" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="I12" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="J12" s="18" t="n">
-        <v>86</v>
-      </c>
-      <c r="K12" s="18" t="n">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1" s="17">
-      <c r="A13" s="13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="13" t="inlineStr">
-        <is>
-          <t>07f180b</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>07f180b9740c0c72f4ff4cb637acce0c8b718efc</t>
-        </is>
-      </c>
-      <c r="D13" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-14 07:21:58</t>
-        </is>
-      </c>
-      <c r="E13" s="13" t="inlineStr">
-        <is>
-          <t>Jevon Zhu</t>
-        </is>
-      </c>
-      <c r="F13" s="13" t="inlineStr">
-        <is>
-          <t>jevonzhu2008@gmail.com</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>修正日报度量值：清理标题围栏并调整年累计完成字段</t>
-        </is>
-      </c>
-      <c r="H13" s="13" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="I13" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="K13" s="13" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1" s="17">
-      <c r="A14" s="18" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>2d4f16f</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>2d4f16fda737382909dd93ca2b175b6618fcbb57</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>2026-10-14 07:01:02</t>
-        </is>
-      </c>
-      <c r="E14" s="18" t="inlineStr">
-        <is>
-          <t>Jevon Zhu</t>
-        </is>
-      </c>
-      <c r="F14" s="18" t="inlineStr">
-        <is>
-          <t>jevonzhu2008@gmail.com</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>新增 KFM日月报语义模型分析报告</t>
-        </is>
-      </c>
-      <c r="H14" s="18" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="I14" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" s="18" t="n">
-        <v>320</v>
-      </c>
-      <c r="K14" s="18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1" s="17">
-      <c r="A15" s="13" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="13" t="inlineStr">
-        <is>
-          <t>5ba71b7</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>5ba71b7bdd8c9fa3140791e2c325425796229e13</t>
-        </is>
-      </c>
-      <c r="D15" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-14 06:57:45</t>
-        </is>
-      </c>
-      <c r="E15" s="13" t="inlineStr">
-        <is>
-          <t>Jevon Zhu</t>
-        </is>
-      </c>
-      <c r="F15" s="13" t="inlineStr">
-        <is>
-          <t>jevonzhu2008@gmail.com</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>修正 DAX/M 代码注释，准确反映实际逻辑</t>
-        </is>
-      </c>
-      <c r="H15" s="13" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="I15" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="J15" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="K15" s="13" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1" s="17">
-      <c r="A16" s="18" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>cea3882</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>cea3882903b1e0ebd284ee0a2acadb18380ddd7f</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="inlineStr">
-        <is>
-          <t>2026-10-14 06:34:36</t>
-        </is>
-      </c>
-      <c r="E16" s="18" t="inlineStr">
-        <is>
-          <t>Jevon Zhu</t>
-        </is>
-      </c>
-      <c r="F16" s="18" t="inlineStr">
-        <is>
-          <t>jevonzhu2008@gmail.com</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>优化语义模型自定义函数命名</t>
-        </is>
-      </c>
-      <c r="H16" s="18" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="I16" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="J16" s="18" t="n">
-        <v>17</v>
-      </c>
-      <c r="K16" s="18" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1" s="17">
-      <c r="A17" s="13" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="13" t="inlineStr">
-        <is>
-          <t>9f32794</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>9f32794cc45bd00e695f720d0e38ca7eda0ee97d</t>
-        </is>
-      </c>
-      <c r="D17" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-14 06:22:46</t>
-        </is>
-      </c>
-      <c r="E17" s="13" t="inlineStr">
-        <is>
-          <t>Jevon Zhu</t>
-        </is>
-      </c>
-      <c r="F17" s="13" t="inlineStr">
-        <is>
-          <t>jevonzhu2008@gmail.com</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>重命名报表项目：KFM选冶厂月报 → L3报表-KFM日月报</t>
-        </is>
-      </c>
-      <c r="H17" s="13" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="I17" s="13" t="n">
-        <v>70</v>
-      </c>
-      <c r="J17" s="13" t="n">
-        <v>695</v>
-      </c>
-      <c r="K17" s="13" t="n">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1" s="17">
-      <c r="A18" s="18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>07301c6</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>07301c63639499dc1642f9abe29a9baee1e0c3cf</t>
-        </is>
-      </c>
-      <c r="D18" s="18" t="inlineStr">
-        <is>
-          <t>2026-10-13 19:57:45</t>
-        </is>
-      </c>
-      <c r="E18" s="18" t="inlineStr">
-        <is>
-          <t>Jevon Zhu</t>
-        </is>
-      </c>
-      <c r="F18" s="18" t="inlineStr">
-        <is>
-          <t>jevonzhu2008@gmail.com</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>修复 KFM选冶厂月报 TMDL 缩进错误</t>
-        </is>
-      </c>
-      <c r="H18" s="18" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="I18" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="K18" s="18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1" s="17">
-      <c r="A19" s="13" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="13" t="inlineStr">
-        <is>
-          <t>1485d55</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>1485d55c4d5b2c241eb05e9040a3897476085331</t>
-        </is>
-      </c>
-      <c r="D19" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-13 19:45:55</t>
-        </is>
-      </c>
-      <c r="E19" s="13" t="inlineStr">
-        <is>
-          <t>Jevon Zhu</t>
-        </is>
-      </c>
-      <c r="F19" s="13" t="inlineStr">
-        <is>
-          <t>jevonzhu2008@gmail.com</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>优化全部 M 查询：步骤名语义化与步骤合并</t>
-        </is>
-      </c>
-      <c r="H19" s="13" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="I19" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="J19" s="13" t="n">
-        <v>134</v>
-      </c>
-      <c r="K19" s="13" t="n">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="20" ht="30" customHeight="1" s="17">
-      <c r="A20" s="18" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>6b4084c</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>6b4084c9a3fb078c53fcbdd2549a2adc1fc7d100</t>
-        </is>
-      </c>
-      <c r="D20" s="18" t="inlineStr">
-        <is>
-          <t>2026-10-13 19:31:50</t>
-        </is>
-      </c>
-      <c r="E20" s="18" t="inlineStr">
-        <is>
-          <t>Jevon Zhu</t>
-        </is>
-      </c>
-      <c r="F20" s="18" t="inlineStr">
-        <is>
-          <t>jevonzhu2008@gmail.com</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>优化L1-KFM日报 M 查询：命名注释与步骤精简</t>
-        </is>
-      </c>
-      <c r="H20" s="18" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="I20" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" s="18" t="n">
-        <v>130</v>
-      </c>
-      <c r="K20" s="18" t="n">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="13" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="13" t="inlineStr">
-        <is>
-          <t>2a59e2f</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>2a59e2f68de3a82d02c6493c75d4a170ce013fae</t>
-        </is>
-      </c>
-      <c r="D21" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-13 19:15:18</t>
-        </is>
-      </c>
-      <c r="E21" s="13" t="inlineStr">
-        <is>
-          <t>Jevon Zhu</t>
-        </is>
-      </c>
-      <c r="F21" s="13" t="inlineStr">
-        <is>
-          <t>jevonzhu2008@gmail.com</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>优化L1-KFM日报 M 查询：内联两个中间表</t>
-        </is>
-      </c>
-      <c r="H21" s="13" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="I21" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="J21" s="13" t="n">
-        <v>21</v>
-      </c>
-      <c r="K21" s="13" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="18" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>48112a2</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>48112a2bfe1b2809ef94fe779a2e7a6c65d60bb2</t>
-        </is>
-      </c>
-      <c r="D22" s="18" t="inlineStr">
-        <is>
-          <t>2026-10-13 18:55:27</t>
-        </is>
-      </c>
-      <c r="E22" s="18" t="inlineStr">
-        <is>
-          <t>Jevon Zhu</t>
-        </is>
-      </c>
-      <c r="F22" s="18" t="inlineStr">
-        <is>
-          <t>jevonzhu2008@gmail.com</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="inlineStr">
-        <is>
-          <t>升级语义模型兼容级别1702，新增日报模型与DAX函数(UDF)</t>
-        </is>
-      </c>
-      <c r="H22" s="18" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="I22" s="18" t="n">
-        <v>35</v>
-      </c>
-      <c r="J22" s="18" t="n">
-        <v>5662</v>
-      </c>
-      <c r="K22" s="18" t="n">
-        <v>771</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="13" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="13" t="inlineStr">
-        <is>
-          <t>69bb2ba</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>69bb2ba9dc7aa839a00235f2ef0ed1b691d7384e</t>
-        </is>
-      </c>
-      <c r="D23" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-13 01:42:09</t>
-        </is>
-      </c>
-      <c r="E23" s="13" t="inlineStr">
-        <is>
-          <t>Jevon Zhu</t>
-        </is>
-      </c>
-      <c r="F23" s="13" t="inlineStr">
-        <is>
-          <t>jevonzhu2008@gmail.com</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>新增项目版本信息 Excel 文档（含项目概述、Git版本历史、提交备注）</t>
-        </is>
-      </c>
-      <c r="H23" s="13" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="I23" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="18" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="18" t="inlineStr">
-        <is>
-          <t>248840e</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>248840e9d232eacba69832ed5401065fb3ce1cab</t>
-        </is>
-      </c>
-      <c r="D24" s="18" t="inlineStr">
-        <is>
-          <t>2026-10-13 01:07:27</t>
-        </is>
-      </c>
-      <c r="E24" s="18" t="inlineStr">
-        <is>
-          <t>Jevon Zhu</t>
-        </is>
-      </c>
-      <c r="F24" s="18" t="inlineStr">
-        <is>
-          <t>jevonzhu2008@gmail.com</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="inlineStr">
-        <is>
-          <t>初始化存档：KFM选冶厂月报 Power BI 项目（PBIP）</t>
-        </is>
-      </c>
-      <c r="H24" s="18" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="I24" s="18" t="n">
+      <c r="I25" s="18" t="n">
         <v>61</v>
       </c>
-      <c r="J24" s="18" t="n">
+      <c r="J25" s="18" t="n">
         <v>26750</v>
       </c>
-      <c r="K24" s="18" t="n">
+      <c r="K25" s="18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2444,7 +2493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A48"/>
+  <dimension ref="A1:A50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="19.95" customHeight="1"/>
   <cols>
     <col width="112" customWidth="1" style="17" min="1" max="1"/>
@@ -2467,12 +2516,31 @@
     <row r="3" ht="19.95" customHeight="1" s="17">
       <c r="A3" t="inlineStr">
         <is>
-          <t>提交 bb50397 ｜ 2026-10-15 16:30:36 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
+          <t>提交 1d1d593 ｜ 2026-10-15 17:39:50 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
     <row r="4" ht="149.55" customHeight="1" s="17">
       <c r="A4" t="inlineStr">
+        <is>
+          <t>修复度量值缺陷并为全部 27 个度量值补充注释，同步分析报告
+- 修复：年累计完成L1 的 SWITCH 兜底 VAR 内联语法错误、钴回收率 RETURN、月报排序键序号集合、日报「二级指标」序号=2 复制粘贴
+- 度量值去掉 v/v_ 草稿前缀，年累计完成L1_v2 已并入年累计完成L1
+- 全部 27 个度量值补充 /// 文档注释（映射 description）
+- 同步更新语义模型分析报告
+Co-Authored-By: Claude Opus 4.8 &lt;noreply@anthropic.com&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="19.95" customHeight="1" s="17">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>提交 bb50397 ｜ 2026-10-15 16:30:36 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="118.5" customHeight="1" s="17">
+      <c r="A6" t="inlineStr">
         <is>
           <t>切换数据源并重构回收率为量×率新口径，合并度量值
 - 参数：SAP BW 服务器 10.43.11.32、系统编号 00、SharePoint 站点切至 cmocco/teams/PBI
@@ -2484,15 +2552,15 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="19.95" customHeight="1" s="17">
-      <c r="A5" t="inlineStr">
+    <row r="7" ht="19.95" customHeight="1" s="17">
+      <c r="A7" t="inlineStr">
         <is>
           <t>提交 3383b89 ｜ 2026-10-15 10:27:59 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="118.5" customHeight="1" s="17">
-      <c r="A6" t="inlineStr">
+    <row r="8" ht="149.55" customHeight="1" s="17">
+      <c r="A8" t="inlineStr">
         <is>
           <t>度量值显示文件夹加数字前缀排序并改名新口径
 - 度量值 displayFolder 加数字前缀：00辅助 / 02月报 / 03日报，「入选品位」改名「01新口径」
@@ -2502,15 +2570,15 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="19.95" customHeight="1" s="17">
-      <c r="A7" t="inlineStr">
+    <row r="9" ht="19.95" customHeight="1" s="17">
+      <c r="A9" t="inlineStr">
         <is>
           <t>提交 03b7f44 ｜ 2026-10-15 10:05:16 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="149.55" customHeight="1" s="17">
-      <c r="A8" t="inlineStr">
+    <row r="10" ht="133.95" customHeight="1" s="17">
+      <c r="A10" t="inlineStr">
         <is>
           <t>二级指标列改名与入选品位/回收率新口径，同步报表与分析报告
 - 语义模型：「类别2」统一改名为「二级指标」，细分逻辑改按序号驱动；序号/排序/环节序号类型统一 int64
@@ -2521,15 +2589,15 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="19.95" customHeight="1" s="17">
-      <c r="A9" s="8" t="inlineStr">
+    <row r="11" ht="19.95" customHeight="1" s="17">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>提交 6e604e4 ｜ 2026-10-14 18:41:35 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="133.95" customHeight="1" s="17">
-      <c r="A10" s="9" t="inlineStr">
+    <row r="12" ht="118.5" customHeight="1" s="17">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>日报表新增入选品位度量值与指标列，同步月报口径、报表页面与分析报告
 - 日报表：新增「指标名称」「产品分类」两列，类别2/排序改按产品分类细分，输出列 15→17
@@ -2541,15 +2609,15 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="19.95" customHeight="1" s="17">
-      <c r="A11" s="8" t="inlineStr">
+    <row r="13" ht="19.95" customHeight="1" s="17">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>提交 d6b1785 ｜ 2026-10-14 14:05:13 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="118.5" customHeight="1" s="17">
-      <c r="A12" s="9" t="inlineStr">
+    <row r="14" ht="118.5" customHeight="1" s="17">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>重命名报表项目：L3报表-KFM日月报 → L3报表
 - 项目、报告、语义模型整体重命名为 L3报表（目录、.pbip、.platform、definition.pbir 同步更新）
@@ -2560,15 +2628,15 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="19.95" customHeight="1" s="17">
-      <c r="A13" s="8" t="inlineStr">
+    <row r="15" ht="19.95" customHeight="1" s="17">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>提交 8c90e31 ｜ 2026-10-14 12:08:57 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="118.5" customHeight="1" s="17">
-      <c r="A14" s="9" t="inlineStr">
+    <row r="16" ht="196.05" customHeight="1" s="17">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>更新语义模型分析报告：同步 M 优化与列精简
 - 模型总览列数同步：月报 18 列、日报 15 列
@@ -2578,15 +2646,15 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="19.95" customHeight="1" s="17">
-      <c r="A15" s="8" t="inlineStr">
+    <row r="17" ht="19.95" customHeight="1" s="17">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>提交 7148b64 ｜ 2026-10-14 11:35:22 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="196.05" customHeight="1" s="17">
-      <c r="A16" s="9" t="inlineStr">
+    <row r="18" ht="118.5" customHeight="1" s="17">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>优化语义模型 M 代码与输出列
 - 日报新增「日期筛选器」列（按「原矿处理量」最大标准日期标记「最近日期」）
@@ -2598,15 +2666,15 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="19.95" customHeight="1" s="17">
-      <c r="A17" s="8" t="inlineStr">
+    <row r="19" ht="19.95" customHeight="1" s="17">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>提交 f996ae9 ｜ 2026-10-14 11:35:16 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="118.5" customHeight="1" s="17">
-      <c r="A18" s="9" t="inlineStr">
+    <row r="20" ht="87.45" customHeight="1" s="17">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>调整报告页面命名与日报日期筛选
 - 页面更名：KFM选冶厂月报UI Enhance → KFM月报UIE、KFM选冶厂月报 → KFM月报
@@ -2617,15 +2685,15 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="19.95" customHeight="1" s="17">
-      <c r="A19" s="8" t="inlineStr">
+    <row r="21" ht="19.95" customHeight="1" s="17">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>提交 630c17f ｜ 2026-10-14 10:06:29 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="87.45" customHeight="1" s="17">
-      <c r="A20" s="9" t="inlineStr">
+    <row r="22" ht="103.05" customHeight="1" s="17">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>更新语义模型分析报告：同步本轮修复
 - 同步年累计完成L1 新口径与新增参数、中间表变化
@@ -2635,15 +2703,15 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="19.95" customHeight="1" s="17">
-      <c r="A21" s="8" t="inlineStr">
+    <row r="23" ht="19.95" customHeight="1" s="17">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>提交 1794160 ｜ 2026-10-14 10:06:24 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="103.05" customHeight="1" s="17">
-      <c r="A22" s="9" t="inlineStr">
+    <row r="24" ht="118.5" customHeight="1" s="17">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>调整报告视觉对象布局与筛选
 - 按钮/书签视觉对象位置与尺寸微调
@@ -2653,15 +2721,15 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="19.95" customHeight="1" s="17">
-      <c r="A23" s="8" t="inlineStr">
+    <row r="25" ht="19.95" customHeight="1" s="17">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>提交 9cbf408 ｜ 2026-10-14 10:06:18 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="118.5" customHeight="1" s="17">
-      <c r="A24" s="9" t="inlineStr">
+    <row r="26" ht="87.45" customHeight="1" s="17">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>修复语义模型分析报告发现的问题
 - 年累计完成L1 口径修正：累计预测数 → 累计实际数（新增列，经上月编码关联月报），消除重复计算
@@ -2676,15 +2744,15 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="19.95" customHeight="1" s="17">
-      <c r="A25" s="8" t="inlineStr">
+    <row r="27" ht="19.95" customHeight="1" s="17">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>提交 07f180b ｜ 2026-10-14 07:21:58 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="87.45" customHeight="1" s="17">
-      <c r="A26" s="9" t="inlineStr">
+    <row r="28" ht="87.45" customHeight="1" s="17">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>修正日报度量值：清理标题围栏并调整年累计完成字段
 - 标题-日报：移除多余的三反引号围栏标记，修复 TMDL 语法解析
@@ -2694,15 +2762,15 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="19.95" customHeight="1" s="17">
-      <c r="A27" s="8" t="inlineStr">
+    <row r="29" ht="19.95" customHeight="1" s="17">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t>提交 2d4f16f ｜ 2026-10-14 07:01:02 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="87.45" customHeight="1" s="17">
-      <c r="A28" s="9" t="inlineStr">
+    <row r="30" ht="103.05" customHeight="1" s="17">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>新增 KFM日月报语义模型分析报告
 HTML 分析报告，涵盖模型总览、M 转换逻辑、DAX 计算逻辑与分级问题清单。
@@ -2710,15 +2778,15 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="19.95" customHeight="1" s="17">
-      <c r="A29" s="8" t="inlineStr">
+    <row r="31" ht="19.95" customHeight="1" s="17">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>提交 5ba71b7 ｜ 2026-10-14 06:57:45 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="103.05" customHeight="1" s="17">
-      <c r="A30" s="9" t="inlineStr">
+    <row r="32" ht="133.95" customHeight="1" s="17">
+      <c r="A32" s="9" t="inlineStr">
         <is>
           <t>修正 DAX/M 代码注释，准确反映实际逻辑
 - functions.tmdl：修正 FormatAmount/FormatRatio 的格式注释（两位小数/差额/百分比），SameMonthPriorYear 顶部注释去掉「年累计实际数」限定
@@ -2727,15 +2795,15 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="19.95" customHeight="1" s="17">
-      <c r="A31" s="8" t="inlineStr">
+    <row r="33" ht="19.95" customHeight="1" s="17">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>提交 cea3882 ｜ 2026-10-14 06:34:36 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="133.95" customHeight="1" s="17">
-      <c r="A32" s="9" t="inlineStr">
+    <row r="34" ht="133.95" customHeight="1" s="17">
+      <c r="A34" s="9" t="inlineStr">
         <is>
           <t>优化语义模型自定义函数命名
 - FormatKFM → FormatAmount（数量格式）
@@ -2745,15 +2813,15 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="19.95" customHeight="1" s="17">
-      <c r="A33" s="8" t="inlineStr">
+    <row r="35" ht="19.95" customHeight="1" s="17">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>提交 9f32794 ｜ 2026-10-14 06:22:46 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="133.95" customHeight="1" s="17">
-      <c r="A34" s="9" t="inlineStr">
+    <row r="36" ht="273.45" customHeight="1" s="17">
+      <c r="A36" s="9" t="inlineStr">
         <is>
           <t>重命名报表项目：KFM选冶厂月报 → L3报表-KFM日月报
 删除旧项目文件，改用新项目名称。
@@ -2761,15 +2829,15 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="19.95" customHeight="1" s="17">
-      <c r="A35" s="8" t="inlineStr">
+    <row r="37" ht="19.95" customHeight="1" s="17">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>提交 07301c6 ｜ 2026-10-13 19:57:45 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="273.45" customHeight="1" s="17">
-      <c r="A36" s="9" t="inlineStr">
+    <row r="38" ht="56.55" customHeight="1" s="17">
+      <c r="A38" s="9" t="inlineStr">
         <is>
           <t>修复 KFM选冶厂月报 TMDL 缩进错误
 将 source 的 M 代码改为三反引号形式，修复 let 顶格导致的 TMDL 缩进解析错误。
@@ -2777,15 +2845,15 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="19.95" customHeight="1" s="17">
-      <c r="A37" s="8" t="inlineStr">
+    <row r="39" ht="19.95" customHeight="1" s="17">
+      <c r="A39" s="8" t="inlineStr">
         <is>
           <t>提交 1485d55 ｜ 2026-10-13 19:45:55 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="56.55" customHeight="1" s="17">
-      <c r="A38" s="9" t="inlineStr">
+    <row r="40" ht="409.6" customHeight="1" s="17">
+      <c r="A40" s="9" t="inlineStr">
         <is>
           <t>优化全部 M 查询：步骤名语义化与步骤合并
 - KFM选冶厂月报：Cube.Transform 直接输出最终列名，删除「重命名列」「新增指标项列」步骤；去掉未使用的产品、矿坑、指标编码维度；合并类别2分组逻辑与最近月份计算；步骤名统一中文
@@ -2794,15 +2862,15 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="19.95" customHeight="1" s="17">
-      <c r="A39" s="8" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="8" t="inlineStr">
         <is>
           <t>提交 6b4084c ｜ 2026-10-13 19:31:50 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="409.6" customHeight="1" s="17">
-      <c r="A40" s="9" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="9" t="inlineStr">
         <is>
           <t>优化L1-KFM日报 M 查询：命名注释与步骤精简
 - Cube.Transform 直接输出最终列名，删除冗余的「重命名的列」步骤
@@ -2813,15 +2881,15 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="8" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="8" t="inlineStr">
         <is>
           <t>提交 2a59e2f ｜ 2026-10-13 19:15:18 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="9" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="9" t="inlineStr">
         <is>
           <t>优化L1-KFM日报 M 查询：内联两个中间表
 - 将 全年预算表、月累计预测表 两个中间表 expression 内联进 L1-KFM日报 的 M 查询，消除跨查询依赖
@@ -2832,15 +2900,15 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="8" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
         <is>
           <t>提交 48112a2 ｜ 2026-10-13 18:55:27 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="9" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="9" t="inlineStr">
         <is>
           <t>升级语义模型兼容级别1702，新增日报模型与DAX函数(UDF)
 语义模型
@@ -2859,30 +2927,30 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="8" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="8" t="inlineStr">
         <is>
           <t>提交 69bb2ba ｜ 2026-10-13 01:42:09 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="9" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="9" t="inlineStr">
         <is>
           <t>新增项目版本信息 Excel 文档（含项目概述、Git版本历史、提交备注）
 Co-Authored-By: Claude Fable 5.1 &lt;noreply@anthropic.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="8" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="8" t="inlineStr">
         <is>
           <t>提交 248840e ｜ 2026-10-13 01:07:27 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="9" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="9" t="inlineStr">
         <is>
           <t>初始化存档：KFM选冶厂月报 Power BI 项目（PBIP）
 项目概述
